--- a/Projects/Pistons_Players_Data_2024-2025.xlsx
+++ b/Projects/Pistons_Players_Data_2024-2025.xlsx
@@ -5,15 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F32AF88F-51FA-C745-A23B-DC5284A5105A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EF60BEA-AF5A-B643-B0E6-5FFA61386524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="580" yWindow="680" windowWidth="28040" windowHeight="17180" xr2:uid="{9F5AD747-0CA0-0449-80A8-FFDBC90AA643}"/>
+    <workbookView xWindow="580" yWindow="680" windowWidth="28040" windowHeight="17180" activeTab="3" xr2:uid="{9F5AD747-0CA0-0449-80A8-FFDBC90AA643}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Roster" sheetId="1" r:id="rId1"/>
+    <sheet name="Regular Season Averages" sheetId="2" r:id="rId2"/>
+    <sheet name="Regular Season Totals" sheetId="3" r:id="rId3"/>
+    <sheet name="Per 36 Minutes" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -35,15 +38,516 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="86">
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>Pos</t>
+  </si>
+  <si>
+    <t>Ht</t>
+  </si>
+  <si>
+    <t>Wt</t>
+  </si>
+  <si>
+    <t>Birth Date</t>
+  </si>
+  <si>
+    <t>Birth</t>
+  </si>
+  <si>
+    <t>Exp</t>
+  </si>
+  <si>
+    <t>College</t>
+  </si>
+  <si>
+    <t>Malik Beasley</t>
+  </si>
+  <si>
+    <t>SG</t>
+  </si>
+  <si>
+    <r>
+      <t>us</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.4"/>
+        <color rgb="FF000000"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t> US</t>
+    </r>
+  </si>
+  <si>
+    <t>Florida State</t>
+  </si>
+  <si>
+    <t>Cade Cunningham</t>
+  </si>
+  <si>
+    <t>PG</t>
+  </si>
+  <si>
+    <t>Oklahoma State</t>
+  </si>
+  <si>
+    <t>Jalen Duren</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Memphis</t>
+  </si>
+  <si>
+    <t>Simone Fontecchio</t>
+  </si>
+  <si>
+    <t>SF</t>
+  </si>
+  <si>
+    <r>
+      <t>it</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.4"/>
+        <color rgb="FF000000"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t> IT</t>
+    </r>
+  </si>
+  <si>
+    <t>Tim Hardaway Jr.</t>
+  </si>
+  <si>
+    <t>Michigan</t>
+  </si>
+  <si>
+    <t>Ron Harper Jr.</t>
+  </si>
+  <si>
+    <t>Rutgers University</t>
+  </si>
+  <si>
+    <t>Tobias Harris</t>
+  </si>
+  <si>
+    <t>PF</t>
+  </si>
+  <si>
+    <t>Tennessee</t>
+  </si>
+  <si>
+    <t>Ron Holland</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Jaden Ivey</t>
+  </si>
+  <si>
+    <t>Purdue</t>
+  </si>
+  <si>
+    <t>Daniss Jenkins</t>
+  </si>
+  <si>
+    <r>
+      <t>University of the Pacific</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.4"/>
+        <color rgb="FF000000"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.4"/>
+        <color rgb="FF3344DD"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>Iona College</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.4"/>
+        <color rgb="FF000000"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.4"/>
+        <color rgb="FF3344DD"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>St. John's</t>
+    </r>
+  </si>
+  <si>
+    <t>Bobi Klintman</t>
+  </si>
+  <si>
+    <r>
+      <t>se</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.4"/>
+        <color rgb="FF000000"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t> SE</t>
+    </r>
+  </si>
+  <si>
+    <t>Wake Forest</t>
+  </si>
+  <si>
+    <t>Wendell Moore Jr.</t>
+  </si>
+  <si>
+    <t>Duke</t>
+  </si>
+  <si>
+    <t>Paul Reed</t>
+  </si>
+  <si>
+    <t>DePaul</t>
+  </si>
+  <si>
+    <t>Marcus Sasser</t>
+  </si>
+  <si>
+    <t>Houston</t>
+  </si>
+  <si>
+    <t>Dennis Schröder</t>
+  </si>
+  <si>
+    <r>
+      <t>de</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.4"/>
+        <color rgb="FF000000"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t> DE</t>
+    </r>
+  </si>
+  <si>
+    <t>Tolu Smith</t>
+  </si>
+  <si>
+    <r>
+      <t>Western Kentucky</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.4"/>
+        <color rgb="FF000000"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.4"/>
+        <color rgb="FF3344DD"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mississippi State</t>
+    </r>
+  </si>
+  <si>
+    <t>Isaiah Stewart</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>Cole Swider</t>
+  </si>
+  <si>
+    <r>
+      <t>Villanova</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.4"/>
+        <color rgb="FF000000"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.4"/>
+        <color rgb="FF3344DD"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>Syracuse</t>
+    </r>
+  </si>
+  <si>
+    <t>Ausar Thompson</t>
+  </si>
+  <si>
+    <t>Lindy Waters III</t>
+  </si>
+  <si>
+    <t>Alondes Williams</t>
+  </si>
+  <si>
+    <r>
+      <t>Triton College</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.4"/>
+        <color rgb="FF000000"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.4"/>
+        <color rgb="FF3344DD"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>Oklahoma</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.4"/>
+        <color rgb="FF000000"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.4"/>
+        <color rgb="FF3344DD"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>Wake Forest</t>
+    </r>
+  </si>
+  <si>
+    <t>Rk</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <t>FG</t>
+  </si>
+  <si>
+    <t>FGA</t>
+  </si>
+  <si>
+    <t>FG%</t>
+  </si>
+  <si>
+    <t>3P</t>
+  </si>
+  <si>
+    <t>3PA</t>
+  </si>
+  <si>
+    <t>3P%</t>
+  </si>
+  <si>
+    <t>2P</t>
+  </si>
+  <si>
+    <t>2PA</t>
+  </si>
+  <si>
+    <t>2P%</t>
+  </si>
+  <si>
+    <t>eFG%</t>
+  </si>
+  <si>
+    <t>FT</t>
+  </si>
+  <si>
+    <t>FTA</t>
+  </si>
+  <si>
+    <t>FT%</t>
+  </si>
+  <si>
+    <t>ORB</t>
+  </si>
+  <si>
+    <t>DRB</t>
+  </si>
+  <si>
+    <t>TRB</t>
+  </si>
+  <si>
+    <t>AST</t>
+  </si>
+  <si>
+    <t>STL</t>
+  </si>
+  <si>
+    <t>BLK</t>
+  </si>
+  <si>
+    <t>TOV</t>
+  </si>
+  <si>
+    <t>PTS</t>
+  </si>
+  <si>
+    <t>Awards</t>
+  </si>
+  <si>
+    <r>
+      <t>MVP-7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.4"/>
+        <color rgb="FF000000"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.4"/>
+        <color rgb="FF3344DD"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.4"/>
+        <color rgb="FF000000"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.4"/>
+        <color rgb="FF3344DD"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>NBA3</t>
+    </r>
+  </si>
+  <si>
+    <t>6MOY-2</t>
+  </si>
+  <si>
+    <t>Trp-Dbl</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.4"/>
+      <color rgb="FF990000"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.4"/>
+      <color rgb="FF000000"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.4"/>
+      <color rgb="FF3344DD"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.4"/>
+      <color rgb="FF000000"/>
+      <name val="Verdana"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -63,13 +567,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -402,9 +916,6804 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{718E304C-1C21-CF42-BAA6-D39930F62F52}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="37.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>5</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="5">
+        <v>46177</v>
+      </c>
+      <c r="E2" s="2">
+        <v>187</v>
+      </c>
+      <c r="F2" s="6">
+        <v>35395</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="2">
+        <v>8</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="5">
+        <v>46179</v>
+      </c>
+      <c r="E3" s="2">
+        <v>220</v>
+      </c>
+      <c r="F3" s="6">
+        <v>37159</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="2">
+        <v>3</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="5">
+        <v>46183</v>
+      </c>
+      <c r="E4" s="2">
+        <v>250</v>
+      </c>
+      <c r="F4" s="6">
+        <v>37943</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="2">
+        <v>2</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>19</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="5">
+        <v>46180</v>
+      </c>
+      <c r="E5" s="2">
+        <v>209</v>
+      </c>
+      <c r="F5" s="6">
+        <v>35042</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="2">
+        <v>2</v>
+      </c>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="5">
+        <v>46178</v>
+      </c>
+      <c r="E6" s="2">
+        <v>205</v>
+      </c>
+      <c r="F6" s="6">
+        <v>33679</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="2">
+        <v>11</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>13</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="5">
+        <v>46178</v>
+      </c>
+      <c r="E7" s="2">
+        <v>233</v>
+      </c>
+      <c r="F7" s="6">
+        <v>36628</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="2">
+        <v>2</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>12</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="5">
+        <v>46181</v>
+      </c>
+      <c r="E8" s="2">
+        <v>226</v>
+      </c>
+      <c r="F8" s="6">
+        <v>33800</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="2">
+        <v>13</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>0</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="5">
+        <v>46181</v>
+      </c>
+      <c r="E9" s="2">
+        <v>206</v>
+      </c>
+      <c r="F9" s="6">
+        <v>38540</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>23</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="5">
+        <v>46176</v>
+      </c>
+      <c r="E10" s="2">
+        <v>195</v>
+      </c>
+      <c r="F10" s="6">
+        <v>37300</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="2">
+        <v>2</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>24</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="5">
+        <v>46177</v>
+      </c>
+      <c r="E11" s="2">
+        <v>165</v>
+      </c>
+      <c r="F11" s="6">
+        <v>37120</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>34</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="5">
+        <v>46182</v>
+      </c>
+      <c r="E12" s="2">
+        <v>225</v>
+      </c>
+      <c r="F12" s="6">
+        <v>37686</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>14</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="5">
+        <v>46178</v>
+      </c>
+      <c r="E13" s="2">
+        <v>215</v>
+      </c>
+      <c r="F13" s="6">
+        <v>37152</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="2">
+        <v>2</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>7</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="5">
+        <v>46182</v>
+      </c>
+      <c r="E14" s="2">
+        <v>210</v>
+      </c>
+      <c r="F14" s="6">
+        <v>36325</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="2">
+        <v>4</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>25</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="5">
+        <v>46174</v>
+      </c>
+      <c r="E15" s="2">
+        <v>195</v>
+      </c>
+      <c r="F15" s="6">
+        <v>36790</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="2">
+        <v>1</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>17</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="5">
+        <v>46174</v>
+      </c>
+      <c r="E16" s="2">
+        <v>175</v>
+      </c>
+      <c r="F16" s="6">
+        <v>34227</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="2">
+        <v>11</v>
+      </c>
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>35</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="5">
+        <v>46184</v>
+      </c>
+      <c r="E17" s="2">
+        <v>254</v>
+      </c>
+      <c r="F17" s="6">
+        <v>36733</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>28</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="5">
+        <v>46181</v>
+      </c>
+      <c r="E18" s="2">
+        <v>250</v>
+      </c>
+      <c r="F18" s="6">
+        <v>37033</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="2">
+        <v>4</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>13</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="5">
+        <v>46183</v>
+      </c>
+      <c r="E19" s="2">
+        <v>220</v>
+      </c>
+      <c r="F19" s="6">
+        <v>36288</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" s="2">
+        <v>2</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>9</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="5">
+        <v>46180</v>
+      </c>
+      <c r="E20" s="2">
+        <v>205</v>
+      </c>
+      <c r="F20" s="6">
+        <v>37651</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="2">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>43</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="5">
+        <v>46178</v>
+      </c>
+      <c r="E21" s="2">
+        <v>210</v>
+      </c>
+      <c r="F21" s="6">
+        <v>35639</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="2">
+        <v>3</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>31</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="5">
+        <v>46177</v>
+      </c>
+      <c r="E22" s="2">
+        <v>210</v>
+      </c>
+      <c r="F22" s="6">
+        <v>36330</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="2">
+        <v>2</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="https://www.basketball-reference.com/players/b/beaslma01.html" xr:uid="{FE4AEA20-B7CF-5A45-9043-EA42BF4DB60E}"/>
+    <hyperlink ref="I2" r:id="rId2" display="https://www.basketball-reference.com/friv/colleges.fcgi?college=floridast" xr:uid="{8D88AA06-7804-7547-B7E9-9E1FC2F631F1}"/>
+    <hyperlink ref="B3" r:id="rId3" display="https://www.basketball-reference.com/players/c/cunnica01.html" xr:uid="{557DE904-1C46-744B-B229-38D12415E628}"/>
+    <hyperlink ref="I3" r:id="rId4" display="https://www.basketball-reference.com/friv/colleges.fcgi?college=okstate" xr:uid="{C5E7B2F7-AB36-084F-9310-3D0C3AE8B52A}"/>
+    <hyperlink ref="B4" r:id="rId5" display="https://www.basketball-reference.com/players/d/durenja01.html" xr:uid="{D7943369-3737-9845-8A2E-678F24B7451C}"/>
+    <hyperlink ref="I4" r:id="rId6" display="https://www.basketball-reference.com/friv/colleges.fcgi?college=memphis" xr:uid="{98D96A2A-C6AA-FC44-8A51-CFC147187387}"/>
+    <hyperlink ref="B5" r:id="rId7" display="https://www.basketball-reference.com/players/f/fontesi01.html" xr:uid="{5123DB3E-6318-B44E-8A7D-56D00E8A54E1}"/>
+    <hyperlink ref="B6" r:id="rId8" display="https://www.basketball-reference.com/players/h/hardati02.html" xr:uid="{68F3F05C-F39A-E641-82E2-EC483D272AF9}"/>
+    <hyperlink ref="I6" r:id="rId9" display="https://www.basketball-reference.com/friv/colleges.fcgi?college=michigan" xr:uid="{AC8DFE5F-E8E3-BE46-91ED-7449D8F77C7A}"/>
+    <hyperlink ref="B7" r:id="rId10" display="https://www.basketball-reference.com/players/h/harpero02.html" xr:uid="{4AB2D8E9-0626-594E-A5D8-53B9DE156849}"/>
+    <hyperlink ref="I7" r:id="rId11" display="https://www.basketball-reference.com/friv/colleges.fcgi?college=rutgers" xr:uid="{DE254FC0-C825-8A4F-BB2B-C39C912079DF}"/>
+    <hyperlink ref="B8" r:id="rId12" display="https://www.basketball-reference.com/players/h/harrito02.html" xr:uid="{3DFD3FB3-5B8D-7C4B-B895-659C9C0D631F}"/>
+    <hyperlink ref="I8" r:id="rId13" display="https://www.basketball-reference.com/friv/colleges.fcgi?college=tennessee" xr:uid="{B2A31054-4302-3F4E-9236-E8598DCC9D20}"/>
+    <hyperlink ref="B9" r:id="rId14" display="https://www.basketball-reference.com/players/h/hollaro01.html" xr:uid="{55EAA6FF-9CF0-C847-B0D3-451A1843A661}"/>
+    <hyperlink ref="B10" r:id="rId15" display="https://www.basketball-reference.com/players/i/iveyja01.html" xr:uid="{0BAF6EAF-1165-ED41-B67E-4592DB1EED97}"/>
+    <hyperlink ref="I10" r:id="rId16" display="https://www.basketball-reference.com/friv/colleges.fcgi?college=purdue" xr:uid="{FD88922F-1EBA-474C-B5B3-A18F8D1308C0}"/>
+    <hyperlink ref="B11" r:id="rId17" display="https://www.basketball-reference.com/players/j/jenkida01.html" xr:uid="{767CA964-D8C1-114D-99B0-244589EB07D6}"/>
+    <hyperlink ref="B12" r:id="rId18" display="https://www.basketball-reference.com/players/k/klintbo01.html" xr:uid="{22F1C9AD-F856-CA44-BC98-FF376754985A}"/>
+    <hyperlink ref="I12" r:id="rId19" display="https://www.basketball-reference.com/friv/colleges.fcgi?college=wake" xr:uid="{E45701E3-A2DC-2C40-BC05-D876D3A3014A}"/>
+    <hyperlink ref="B13" r:id="rId20" display="https://www.basketball-reference.com/players/m/moorewe01.html" xr:uid="{F6498C7C-E8A1-5C44-94EF-08516E90020A}"/>
+    <hyperlink ref="I13" r:id="rId21" display="https://www.basketball-reference.com/friv/colleges.fcgi?college=duke" xr:uid="{5380A3BD-C298-7148-8690-895D5D1F9FB7}"/>
+    <hyperlink ref="B14" r:id="rId22" display="https://www.basketball-reference.com/players/r/reedpa01.html" xr:uid="{58277A41-CB13-D34E-988A-AB64B301A45C}"/>
+    <hyperlink ref="I14" r:id="rId23" display="https://www.basketball-reference.com/friv/colleges.fcgi?college=depaul" xr:uid="{701DA30F-7A28-544F-8725-E88CF39DB1DB}"/>
+    <hyperlink ref="B15" r:id="rId24" display="https://www.basketball-reference.com/players/s/sassema01.html" xr:uid="{D4E29318-F720-5541-8663-5A62CC52EC32}"/>
+    <hyperlink ref="I15" r:id="rId25" display="https://www.basketball-reference.com/friv/colleges.fcgi?college=houston" xr:uid="{C413E892-6279-8840-A069-ABCFBCD53536}"/>
+    <hyperlink ref="B16" r:id="rId26" display="https://www.basketball-reference.com/players/s/schrode01.html" xr:uid="{C1B34841-3284-CB45-B6BB-F6DDEC37F288}"/>
+    <hyperlink ref="B17" r:id="rId27" display="https://www.basketball-reference.com/players/s/smithto05.html" xr:uid="{A5A9C3E9-97EB-2D40-9220-8A13F797F5E3}"/>
+    <hyperlink ref="B18" r:id="rId28" display="https://www.basketball-reference.com/players/s/stewais01.html" xr:uid="{64D1A496-BE88-B946-B8A7-7492A20675A5}"/>
+    <hyperlink ref="I18" r:id="rId29" display="https://www.basketball-reference.com/friv/colleges.fcgi?college=washington" xr:uid="{67367A0B-ACE9-F944-8CC1-EA63BCCFA40A}"/>
+    <hyperlink ref="B19" r:id="rId30" display="https://www.basketball-reference.com/players/s/swideco01.html" xr:uid="{A41BE459-52CD-AA49-AB02-8310C1228469}"/>
+    <hyperlink ref="B20" r:id="rId31" display="https://www.basketball-reference.com/players/t/thompau01.html" xr:uid="{DEC01804-BB1F-5946-BFE3-023961CDFC9A}"/>
+    <hyperlink ref="B21" r:id="rId32" display="https://www.basketball-reference.com/players/w/waterli01.html" xr:uid="{252849F4-5C81-C04D-B46A-A4D620C7A0C4}"/>
+    <hyperlink ref="I21" r:id="rId33" display="https://www.basketball-reference.com/friv/colleges.fcgi?college=okstate" xr:uid="{9DBBE5DE-3709-5E40-A074-0010365D3927}"/>
+    <hyperlink ref="B22" r:id="rId34" display="https://www.basketball-reference.com/players/w/willial06.html" xr:uid="{5D02268E-D9E2-FD47-B932-1F0DC99FA65B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32DB2531-B10A-8044-8961-4025511EEEA0}">
+  <dimension ref="A1:AD22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2">
+        <v>70</v>
+      </c>
+      <c r="F2" s="2">
+        <v>70</v>
+      </c>
+      <c r="G2" s="2">
+        <v>35</v>
+      </c>
+      <c r="H2" s="2">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="I2" s="2">
+        <v>20.8</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="K2" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="L2" s="2">
+        <v>6</v>
+      </c>
+      <c r="M2" s="2">
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="N2" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="O2" s="2">
+        <v>14.8</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>0.52100000000000002</v>
+      </c>
+      <c r="R2" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="S2" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="T2" s="2">
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="U2" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="V2" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="W2" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="X2" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>26.1</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2">
+        <v>32</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="2">
+        <v>73</v>
+      </c>
+      <c r="F3" s="2">
+        <v>73</v>
+      </c>
+      <c r="G3" s="2">
+        <v>31.6</v>
+      </c>
+      <c r="H3" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="I3" s="2">
+        <v>11</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.47699999999999998</v>
+      </c>
+      <c r="K3" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="L3" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="N3" s="2">
+        <v>4</v>
+      </c>
+      <c r="O3" s="2">
+        <v>7.4</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="R3" s="2">
+        <v>2</v>
+      </c>
+      <c r="S3" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="T3" s="2">
+        <v>0.86099999999999999</v>
+      </c>
+      <c r="U3" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="V3" s="2">
+        <v>5</v>
+      </c>
+      <c r="W3" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="X3" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Y3" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="AA3" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>13.7</v>
+      </c>
+      <c r="AD3" s="2"/>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="2">
+        <v>22</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2">
+        <v>30</v>
+      </c>
+      <c r="F4" s="2">
+        <v>30</v>
+      </c>
+      <c r="G4" s="2">
+        <v>29.9</v>
+      </c>
+      <c r="H4" s="2">
+        <v>6.3</v>
+      </c>
+      <c r="I4" s="2">
+        <v>13.8</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.46</v>
+      </c>
+      <c r="K4" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="L4" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="N4" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="O4" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0.49</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0.53600000000000003</v>
+      </c>
+      <c r="R4" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="S4" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="T4" s="2">
+        <v>0.73299999999999998</v>
+      </c>
+      <c r="U4" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="V4" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="W4" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="X4" s="2">
+        <v>4</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="AA4" s="2">
+        <v>3</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="AD4" s="2"/>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2">
+        <v>32</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2">
+        <v>77</v>
+      </c>
+      <c r="F5" s="2">
+        <v>77</v>
+      </c>
+      <c r="G5" s="2">
+        <v>28</v>
+      </c>
+      <c r="H5" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="I5" s="2">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.40600000000000003</v>
+      </c>
+      <c r="K5" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="L5" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0.36799999999999999</v>
+      </c>
+      <c r="N5" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="O5" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0.48399999999999999</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="R5" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="S5" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="T5" s="2">
+        <v>0.85499999999999998</v>
+      </c>
+      <c r="U5" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="V5" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="W5" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="X5" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="Y5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="AA5" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="AB5" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="AC5" s="2">
+        <v>11</v>
+      </c>
+      <c r="AD5" s="2"/>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2">
+        <v>28</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="8">
+        <v>82</v>
+      </c>
+      <c r="F6" s="2">
+        <v>18</v>
+      </c>
+      <c r="G6" s="2">
+        <v>27.8</v>
+      </c>
+      <c r="H6" s="2">
+        <v>5.6</v>
+      </c>
+      <c r="I6" s="2">
+        <v>13.1</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.43</v>
+      </c>
+      <c r="K6" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="L6" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="M6" s="2">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="N6" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="O6" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>0.57899999999999996</v>
+      </c>
+      <c r="R6" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="S6" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="T6" s="2">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="U6" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="V6" s="2">
+        <v>2</v>
+      </c>
+      <c r="W6" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="X6" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="Y6" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="AC6" s="2">
+        <v>16.3</v>
+      </c>
+      <c r="AD6" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2">
+        <v>21</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2">
+        <v>78</v>
+      </c>
+      <c r="F7" s="2">
+        <v>78</v>
+      </c>
+      <c r="G7" s="2">
+        <v>26.1</v>
+      </c>
+      <c r="H7" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="O7" s="2">
+        <v>7</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="R7" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="S7" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="T7" s="2">
+        <v>0.66900000000000004</v>
+      </c>
+      <c r="U7" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="V7" s="2">
+        <v>6.8</v>
+      </c>
+      <c r="W7" s="2">
+        <v>10.3</v>
+      </c>
+      <c r="X7" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="AB7" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>11.8</v>
+      </c>
+      <c r="AD7" s="2"/>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="2">
+        <v>31</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="2">
+        <v>28</v>
+      </c>
+      <c r="F8" s="2">
+        <v>8</v>
+      </c>
+      <c r="G8" s="2">
+        <v>25.2</v>
+      </c>
+      <c r="H8" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="I8" s="2">
+        <v>9</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.378</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L8" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="M8" s="2">
+        <v>0.30199999999999999</v>
+      </c>
+      <c r="N8" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="O8" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0.434</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>0.442</v>
+      </c>
+      <c r="R8" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="S8" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="T8" s="2">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="U8" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="V8" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="W8" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="X8" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="AB8" s="2">
+        <v>2</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="AD8" s="2"/>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="2">
+        <v>22</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="2">
+        <v>59</v>
+      </c>
+      <c r="F9" s="2">
+        <v>48</v>
+      </c>
+      <c r="G9" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="H9" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7.8</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0.224</v>
+      </c>
+      <c r="N9" s="2">
+        <v>4</v>
+      </c>
+      <c r="O9" s="2">
+        <v>7</v>
+      </c>
+      <c r="P9" s="2">
+        <v>0.57199999999999995</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="R9" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="S9" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="T9" s="2">
+        <v>0.64100000000000001</v>
+      </c>
+      <c r="U9" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="V9" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="W9" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X9" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="AB9" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="AC9" s="2">
+        <v>10.1</v>
+      </c>
+      <c r="AD9" s="2"/>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="2">
+        <v>24</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>22</v>
+      </c>
+      <c r="H10" s="2">
+        <v>6</v>
+      </c>
+      <c r="I10" s="2">
+        <v>9</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="K10" s="2">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2">
+        <v>6</v>
+      </c>
+      <c r="O10" s="2">
+        <v>9</v>
+      </c>
+      <c r="P10" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="R10" s="2">
+        <v>2</v>
+      </c>
+      <c r="S10" s="2">
+        <v>3</v>
+      </c>
+      <c r="T10" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="U10" s="2">
+        <v>4</v>
+      </c>
+      <c r="V10" s="2">
+        <v>4</v>
+      </c>
+      <c r="W10" s="2">
+        <v>8</v>
+      </c>
+      <c r="X10" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="2">
+        <v>2</v>
+      </c>
+      <c r="AB10" s="2">
+        <v>3</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>14</v>
+      </c>
+      <c r="AD10" s="2"/>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="2">
+        <v>23</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="2">
+        <v>72</v>
+      </c>
+      <c r="F11" s="2">
+        <v>4</v>
+      </c>
+      <c r="G11" s="2">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="H11" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="I11" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.55900000000000005</v>
+      </c>
+      <c r="K11" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="N11" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="O11" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="P11" s="2">
+        <v>0.60699999999999998</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>0.58599999999999997</v>
+      </c>
+      <c r="R11" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="S11" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="T11" s="2">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="U11" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="V11" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="W11" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="X11" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="Z11" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="AA11" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="AB11" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="AC11" s="2">
+        <v>6</v>
+      </c>
+      <c r="AD11" s="2"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="2">
+        <v>24</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>17</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2">
+        <v>6</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2">
+        <v>1</v>
+      </c>
+      <c r="O12" s="2">
+        <v>2</v>
+      </c>
+      <c r="P12" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="R12" s="2">
+        <v>2</v>
+      </c>
+      <c r="S12" s="2">
+        <v>2</v>
+      </c>
+      <c r="T12" s="2">
+        <v>1</v>
+      </c>
+      <c r="U12" s="2">
+        <v>4</v>
+      </c>
+      <c r="V12" s="2">
+        <v>3</v>
+      </c>
+      <c r="W12" s="2">
+        <v>7</v>
+      </c>
+      <c r="X12" s="2">
+        <v>2</v>
+      </c>
+      <c r="Y12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="2">
+        <v>4</v>
+      </c>
+      <c r="AD12" s="2"/>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="2">
+        <v>29</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="2">
+        <v>75</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
+        <v>16.5</v>
+      </c>
+      <c r="H13" s="2">
+        <v>2</v>
+      </c>
+      <c r="I13" s="2">
+        <v>5</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0.40200000000000002</v>
+      </c>
+      <c r="K13" s="2">
+        <v>1</v>
+      </c>
+      <c r="L13" s="2">
+        <v>3</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="N13" s="2">
+        <v>1</v>
+      </c>
+      <c r="O13" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="P13" s="2">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>0.504</v>
+      </c>
+      <c r="R13" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="S13" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="T13" s="2">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="U13" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="V13" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="W13" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="X13" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="Y13" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="Z13" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA13" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="AB13" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="AC13" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="AD13" s="2"/>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="2">
+        <v>19</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="2">
+        <v>81</v>
+      </c>
+      <c r="F14" s="2">
+        <v>2</v>
+      </c>
+      <c r="G14" s="2">
+        <v>15.6</v>
+      </c>
+      <c r="H14" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="I14" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="K14" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="L14" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="M14" s="2">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="N14" s="2">
+        <v>2</v>
+      </c>
+      <c r="O14" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="P14" s="2">
+        <v>0.60799999999999998</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>0.51700000000000002</v>
+      </c>
+      <c r="R14" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="S14" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="T14" s="2">
+        <v>0.754</v>
+      </c>
+      <c r="U14" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="V14" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="W14" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="X14" s="2">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="Z14" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA14" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="AB14" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="AC14" s="2">
+        <v>6.4</v>
+      </c>
+      <c r="AD14" s="2"/>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="2">
+        <v>24</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="2">
+        <v>57</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>14.2</v>
+      </c>
+      <c r="H15" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="I15" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0.46300000000000002</v>
+      </c>
+      <c r="K15" s="2">
+        <v>1</v>
+      </c>
+      <c r="L15" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="M15" s="2">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="N15" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="O15" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="P15" s="2">
+        <v>0.54900000000000004</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="R15" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="S15" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="T15" s="2">
+        <v>0.84299999999999997</v>
+      </c>
+      <c r="U15" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="V15" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="W15" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="X15" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="Y15" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="Z15" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="AA15" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="AB15" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="AC15" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="AD15" s="2"/>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="2">
+        <v>23</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="2">
+        <v>20</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2">
+        <v>11</v>
+      </c>
+      <c r="H16" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="I16" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0.46</v>
+      </c>
+      <c r="K16" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="L16" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="M16" s="2">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="N16" s="2">
+        <v>1</v>
+      </c>
+      <c r="O16" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="P16" s="2">
+        <v>0.52800000000000002</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="R16" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="S16" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="T16" s="2">
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="U16" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="V16" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="W16" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="X16" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="Y16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Z16" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AB16" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="AC16" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="AD16" s="2"/>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="2">
+        <v>25</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="2">
+        <v>45</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="H17" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="I17" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="K17" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="L17" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="M17" s="2">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="N17" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="O17" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="P17" s="2">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="R17" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="S17" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="T17" s="2">
+        <v>0.76200000000000001</v>
+      </c>
+      <c r="U17" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="V17" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="W17" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="X17" s="2">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="Z17" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="AB17" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="AC17" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AD17" s="2"/>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="2">
+        <v>27</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="2">
+        <v>14</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="H18" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I18" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L18" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="M18" s="2">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="N18" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="O18" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="P18" s="2">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="R18" s="2">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2">
+        <v>0</v>
+      </c>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="V18" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="W18" s="2">
+        <v>1</v>
+      </c>
+      <c r="X18" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="Y18" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="Z18" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="AA18" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AB18" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AC18" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="AD18" s="2"/>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="2">
+        <v>25</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="M19" s="2">
+        <v>0</v>
+      </c>
+      <c r="N19" s="2">
+        <v>0</v>
+      </c>
+      <c r="O19" s="2">
+        <v>0</v>
+      </c>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2">
+        <v>0</v>
+      </c>
+      <c r="R19" s="2">
+        <v>0</v>
+      </c>
+      <c r="S19" s="2">
+        <v>0</v>
+      </c>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2">
+        <v>1</v>
+      </c>
+      <c r="W19" s="2">
+        <v>1</v>
+      </c>
+      <c r="X19" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Y19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AC19" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="2"/>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="2">
+        <v>21</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="2">
+        <v>8</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="I20" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="K20" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="L20" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="M20" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="N20" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="O20" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="P20" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="R20" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="S20" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="T20" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="U20" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="V20" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="W20" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="X20" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="Y20" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="Z20" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="AA20" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="AB20" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="AD20" s="2"/>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="2">
+        <v>25</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
+        <v>4</v>
+      </c>
+      <c r="H21" s="2">
+        <v>2</v>
+      </c>
+      <c r="I21" s="2">
+        <v>2</v>
+      </c>
+      <c r="J21" s="2">
+        <v>1</v>
+      </c>
+      <c r="K21" s="2">
+        <v>1</v>
+      </c>
+      <c r="L21" s="2">
+        <v>1</v>
+      </c>
+      <c r="M21" s="2">
+        <v>1</v>
+      </c>
+      <c r="N21" s="2">
+        <v>1</v>
+      </c>
+      <c r="O21" s="2">
+        <v>1</v>
+      </c>
+      <c r="P21" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="R21" s="2">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2">
+        <v>0</v>
+      </c>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2">
+        <v>0</v>
+      </c>
+      <c r="W21" s="2">
+        <v>0</v>
+      </c>
+      <c r="X21" s="2">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="2">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="2"/>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="2">
+        <v>23</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="2">
+        <v>7</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="H22" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="I22" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="K22" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="L22" s="2">
+        <v>1</v>
+      </c>
+      <c r="M22" s="2">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="N22" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="O22" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="P22" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="R22" s="2">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="T22" s="2">
+        <v>0</v>
+      </c>
+      <c r="U22" s="2">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="W22" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="X22" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="Y22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="AB22" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="AC22" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD22" s="2"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="https://www.basketball-reference.com/players/c/cunnica01.html" xr:uid="{6A23318B-1452-3A4E-A11E-27F088BEBC39}"/>
+    <hyperlink ref="B3" r:id="rId2" display="https://www.basketball-reference.com/players/h/harrito02.html" xr:uid="{6BBD7B49-A614-F64F-AD85-F8DA1792A7FF}"/>
+    <hyperlink ref="B4" r:id="rId3" display="https://www.basketball-reference.com/players/i/iveyja01.html" xr:uid="{1AA32CB2-60CB-A142-82C7-AFFFA15E833B}"/>
+    <hyperlink ref="B5" r:id="rId4" display="https://www.basketball-reference.com/players/h/hardati02.html" xr:uid="{01CFBC29-E43B-2344-B22C-D3B781ABA9E6}"/>
+    <hyperlink ref="B6" r:id="rId5" display="https://www.basketball-reference.com/players/b/beaslma01.html" xr:uid="{3AA9F9B2-0086-AE40-A9BC-7CD12A74CEBB}"/>
+    <hyperlink ref="AD6" r:id="rId6" location="all_smoy" display="https://www.basketball-reference.com/awards/awards_2025.html - all_smoy" xr:uid="{50B875BC-5684-A242-B7BF-8C4CA02B8E2A}"/>
+    <hyperlink ref="B7" r:id="rId7" display="https://www.basketball-reference.com/players/d/durenja01.html" xr:uid="{38B3A041-2406-5E4D-832C-5589C9B60138}"/>
+    <hyperlink ref="B8" r:id="rId8" display="https://www.basketball-reference.com/players/s/schrode01.html" xr:uid="{9E254C51-9A0B-4345-9D2D-65188394C7A9}"/>
+    <hyperlink ref="B9" r:id="rId9" display="https://www.basketball-reference.com/players/t/thompau01.html" xr:uid="{DACBCCBC-EFCE-2E44-839C-60C496A2B1B5}"/>
+    <hyperlink ref="B10" r:id="rId10" display="https://www.basketball-reference.com/players/s/smithto05.html" xr:uid="{3BF88D3F-4303-704E-9808-5341A1DB51EB}"/>
+    <hyperlink ref="B11" r:id="rId11" display="https://www.basketball-reference.com/players/s/stewais01.html" xr:uid="{1C5C54A9-3F85-4049-8C56-D71A2B592C35}"/>
+    <hyperlink ref="B12" r:id="rId12" display="https://www.basketball-reference.com/players/h/harpero02.html" xr:uid="{A4E78B13-BE91-E445-82D9-C3791731D67E}"/>
+    <hyperlink ref="B13" r:id="rId13" display="https://www.basketball-reference.com/players/f/fontesi01.html" xr:uid="{68C554E9-94E4-F047-BCC6-D36FA9F40F96}"/>
+    <hyperlink ref="B14" r:id="rId14" display="https://www.basketball-reference.com/players/h/hollaro01.html" xr:uid="{8716CD87-88FB-B34A-9B53-F338E8CC18F6}"/>
+    <hyperlink ref="B15" r:id="rId15" display="https://www.basketball-reference.com/players/s/sassema01.html" xr:uid="{FB3798F2-CFAC-9945-BA82-E1658DF15B14}"/>
+    <hyperlink ref="B16" r:id="rId16" display="https://www.basketball-reference.com/players/m/moorewe01.html" xr:uid="{8E0F531F-605B-E347-BB24-F157DCB16420}"/>
+    <hyperlink ref="B17" r:id="rId17" display="https://www.basketball-reference.com/players/r/reedpa01.html" xr:uid="{40D77FBC-4D95-DF45-8C49-8CE9099DDCAD}"/>
+    <hyperlink ref="B18" r:id="rId18" display="https://www.basketball-reference.com/players/w/waterli01.html" xr:uid="{8D16F522-CF3E-1343-B51F-4392416C396E}"/>
+    <hyperlink ref="B19" r:id="rId19" display="https://www.basketball-reference.com/players/s/swideco01.html" xr:uid="{5FE0344A-2ED4-D740-B316-6E9C1F73AC26}"/>
+    <hyperlink ref="B20" r:id="rId20" display="https://www.basketball-reference.com/players/k/klintbo01.html" xr:uid="{17F22BF5-5978-8E43-B9E8-B8B576F397D9}"/>
+    <hyperlink ref="B21" r:id="rId21" display="https://www.basketball-reference.com/players/w/willial06.html" xr:uid="{5006CDDE-FF17-CA47-A4F4-68CE6AA6E936}"/>
+    <hyperlink ref="B22" r:id="rId22" display="https://www.basketball-reference.com/players/j/jenkida01.html" xr:uid="{334E2C37-4FBC-4449-8333-B7EED684780A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A247BE8-FDAC-924F-8711-90D37CD694D2}">
+  <dimension ref="A1:AD22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2">
+        <v>70</v>
+      </c>
+      <c r="E2" s="2">
+        <v>70</v>
+      </c>
+      <c r="F2" s="2">
+        <v>2452</v>
+      </c>
+      <c r="G2" s="2">
+        <v>684</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1457</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="J2" s="2">
+        <v>149</v>
+      </c>
+      <c r="K2" s="2">
+        <v>418</v>
+      </c>
+      <c r="L2" s="2">
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="M2" s="2">
+        <v>535</v>
+      </c>
+      <c r="N2" s="2">
+        <v>1039</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0.52100000000000002</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>313</v>
+      </c>
+      <c r="R2" s="2">
+        <v>370</v>
+      </c>
+      <c r="S2" s="2">
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="T2" s="2">
+        <v>56</v>
+      </c>
+      <c r="U2" s="2">
+        <v>369</v>
+      </c>
+      <c r="V2" s="2">
+        <v>425</v>
+      </c>
+      <c r="W2" s="2">
+        <v>638</v>
+      </c>
+      <c r="X2" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>53</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>309</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>195</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>1830</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>9</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2">
+        <v>32</v>
+      </c>
+      <c r="D3" s="2">
+        <v>73</v>
+      </c>
+      <c r="E3" s="2">
+        <v>73</v>
+      </c>
+      <c r="F3" s="2">
+        <v>2305</v>
+      </c>
+      <c r="G3" s="2">
+        <v>384</v>
+      </c>
+      <c r="H3" s="2">
+        <v>805</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0.47699999999999998</v>
+      </c>
+      <c r="J3" s="2">
+        <v>91</v>
+      </c>
+      <c r="K3" s="2">
+        <v>264</v>
+      </c>
+      <c r="L3" s="2">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="M3" s="2">
+        <v>293</v>
+      </c>
+      <c r="N3" s="2">
+        <v>541</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>143</v>
+      </c>
+      <c r="R3" s="2">
+        <v>166</v>
+      </c>
+      <c r="S3" s="2">
+        <v>0.86099999999999999</v>
+      </c>
+      <c r="T3" s="2">
+        <v>65</v>
+      </c>
+      <c r="U3" s="2">
+        <v>367</v>
+      </c>
+      <c r="V3" s="2">
+        <v>432</v>
+      </c>
+      <c r="W3" s="2">
+        <v>162</v>
+      </c>
+      <c r="X3" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y3" s="2">
+        <v>57</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA3" s="2">
+        <v>138</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>1002</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="2"/>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2">
+        <v>28</v>
+      </c>
+      <c r="D4" s="8">
+        <v>82</v>
+      </c>
+      <c r="E4" s="2">
+        <v>18</v>
+      </c>
+      <c r="F4" s="2">
+        <v>2283</v>
+      </c>
+      <c r="G4" s="2">
+        <v>461</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1071</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0.43</v>
+      </c>
+      <c r="J4" s="2">
+        <v>319</v>
+      </c>
+      <c r="K4" s="2">
+        <v>766</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="M4" s="2">
+        <v>142</v>
+      </c>
+      <c r="N4" s="2">
+        <v>305</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0.57899999999999996</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>95</v>
+      </c>
+      <c r="R4" s="2">
+        <v>140</v>
+      </c>
+      <c r="S4" s="2">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="T4" s="2">
+        <v>47</v>
+      </c>
+      <c r="U4" s="2">
+        <v>167</v>
+      </c>
+      <c r="V4" s="2">
+        <v>214</v>
+      </c>
+      <c r="W4" s="2">
+        <v>139</v>
+      </c>
+      <c r="X4" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>5</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA4" s="2">
+        <v>125</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>1336</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2">
+        <v>32</v>
+      </c>
+      <c r="D5" s="2">
+        <v>77</v>
+      </c>
+      <c r="E5" s="2">
+        <v>77</v>
+      </c>
+      <c r="F5" s="2">
+        <v>2153</v>
+      </c>
+      <c r="G5" s="2">
+        <v>276</v>
+      </c>
+      <c r="H5" s="2">
+        <v>680</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.40600000000000003</v>
+      </c>
+      <c r="J5" s="2">
+        <v>168</v>
+      </c>
+      <c r="K5" s="2">
+        <v>457</v>
+      </c>
+      <c r="L5" s="2">
+        <v>0.36799999999999999</v>
+      </c>
+      <c r="M5" s="2">
+        <v>108</v>
+      </c>
+      <c r="N5" s="2">
+        <v>223</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0.48399999999999999</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>124</v>
+      </c>
+      <c r="R5" s="2">
+        <v>145</v>
+      </c>
+      <c r="S5" s="2">
+        <v>0.85499999999999998</v>
+      </c>
+      <c r="T5" s="2">
+        <v>18</v>
+      </c>
+      <c r="U5" s="2">
+        <v>165</v>
+      </c>
+      <c r="V5" s="2">
+        <v>183</v>
+      </c>
+      <c r="W5" s="2">
+        <v>123</v>
+      </c>
+      <c r="X5" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y5" s="2">
+        <v>7</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>48</v>
+      </c>
+      <c r="AA5" s="2">
+        <v>96</v>
+      </c>
+      <c r="AB5" s="2">
+        <v>844</v>
+      </c>
+      <c r="AC5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="2"/>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2">
+        <v>21</v>
+      </c>
+      <c r="D6" s="2">
+        <v>78</v>
+      </c>
+      <c r="E6" s="2">
+        <v>78</v>
+      </c>
+      <c r="F6" s="2">
+        <v>2034</v>
+      </c>
+      <c r="G6" s="2">
+        <v>378</v>
+      </c>
+      <c r="H6" s="2">
+        <v>546</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2">
+        <v>378</v>
+      </c>
+      <c r="N6" s="2">
+        <v>546</v>
+      </c>
+      <c r="O6" s="2">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>162</v>
+      </c>
+      <c r="R6" s="2">
+        <v>242</v>
+      </c>
+      <c r="S6" s="2">
+        <v>0.66900000000000004</v>
+      </c>
+      <c r="T6" s="2">
+        <v>277</v>
+      </c>
+      <c r="U6" s="2">
+        <v>530</v>
+      </c>
+      <c r="V6" s="2">
+        <v>807</v>
+      </c>
+      <c r="W6" s="2">
+        <v>209</v>
+      </c>
+      <c r="X6" s="2">
+        <v>54</v>
+      </c>
+      <c r="Y6" s="2">
+        <v>89</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>136</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>251</v>
+      </c>
+      <c r="AB6" s="2">
+        <v>918</v>
+      </c>
+      <c r="AC6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="2"/>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="2">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2">
+        <v>72</v>
+      </c>
+      <c r="E7" s="2">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1434</v>
+      </c>
+      <c r="G7" s="2">
+        <v>176</v>
+      </c>
+      <c r="H7" s="2">
+        <v>315</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.55900000000000005</v>
+      </c>
+      <c r="J7" s="2">
+        <v>17</v>
+      </c>
+      <c r="K7" s="2">
+        <v>53</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="M7" s="2">
+        <v>159</v>
+      </c>
+      <c r="N7" s="2">
+        <v>262</v>
+      </c>
+      <c r="O7" s="2">
+        <v>0.60699999999999998</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0.58599999999999997</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>66</v>
+      </c>
+      <c r="R7" s="2">
+        <v>87</v>
+      </c>
+      <c r="S7" s="2">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="T7" s="2">
+        <v>130</v>
+      </c>
+      <c r="U7" s="2">
+        <v>269</v>
+      </c>
+      <c r="V7" s="2">
+        <v>399</v>
+      </c>
+      <c r="W7" s="2">
+        <v>123</v>
+      </c>
+      <c r="X7" s="2">
+        <v>28</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>101</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>68</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>183</v>
+      </c>
+      <c r="AB7" s="2">
+        <v>435</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="2"/>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="2">
+        <v>22</v>
+      </c>
+      <c r="D8" s="2">
+        <v>59</v>
+      </c>
+      <c r="E8" s="2">
+        <v>48</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1328</v>
+      </c>
+      <c r="G8" s="2">
+        <v>246</v>
+      </c>
+      <c r="H8" s="2">
+        <v>460</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="J8" s="2">
+        <v>11</v>
+      </c>
+      <c r="K8" s="2">
+        <v>49</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0.224</v>
+      </c>
+      <c r="M8" s="2">
+        <v>235</v>
+      </c>
+      <c r="N8" s="2">
+        <v>411</v>
+      </c>
+      <c r="O8" s="2">
+        <v>0.57199999999999995</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>91</v>
+      </c>
+      <c r="R8" s="2">
+        <v>142</v>
+      </c>
+      <c r="S8" s="2">
+        <v>0.64100000000000001</v>
+      </c>
+      <c r="T8" s="2">
+        <v>111</v>
+      </c>
+      <c r="U8" s="2">
+        <v>192</v>
+      </c>
+      <c r="V8" s="2">
+        <v>303</v>
+      </c>
+      <c r="W8" s="2">
+        <v>134</v>
+      </c>
+      <c r="X8" s="2">
+        <v>98</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>164</v>
+      </c>
+      <c r="AB8" s="2">
+        <v>594</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="2"/>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="2">
+        <v>19</v>
+      </c>
+      <c r="D9" s="2">
+        <v>81</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1266</v>
+      </c>
+      <c r="G9" s="2">
+        <v>197</v>
+      </c>
+      <c r="H9" s="2">
+        <v>416</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="J9" s="2">
+        <v>36</v>
+      </c>
+      <c r="K9" s="2">
+        <v>151</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="M9" s="2">
+        <v>161</v>
+      </c>
+      <c r="N9" s="2">
+        <v>265</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0.60799999999999998</v>
+      </c>
+      <c r="P9" s="2">
+        <v>0.51700000000000002</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>92</v>
+      </c>
+      <c r="R9" s="2">
+        <v>122</v>
+      </c>
+      <c r="S9" s="2">
+        <v>0.754</v>
+      </c>
+      <c r="T9" s="2">
+        <v>40</v>
+      </c>
+      <c r="U9" s="2">
+        <v>178</v>
+      </c>
+      <c r="V9" s="2">
+        <v>218</v>
+      </c>
+      <c r="W9" s="2">
+        <v>82</v>
+      </c>
+      <c r="X9" s="2">
+        <v>49</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>17</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>141</v>
+      </c>
+      <c r="AB9" s="2">
+        <v>522</v>
+      </c>
+      <c r="AC9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="2"/>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="2">
+        <v>29</v>
+      </c>
+      <c r="D10" s="2">
+        <v>75</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1237</v>
+      </c>
+      <c r="G10" s="2">
+        <v>150</v>
+      </c>
+      <c r="H10" s="2">
+        <v>373</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0.40200000000000002</v>
+      </c>
+      <c r="J10" s="2">
+        <v>76</v>
+      </c>
+      <c r="K10" s="2">
+        <v>227</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="M10" s="2">
+        <v>74</v>
+      </c>
+      <c r="N10" s="2">
+        <v>146</v>
+      </c>
+      <c r="O10" s="2">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="P10" s="2">
+        <v>0.504</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>70</v>
+      </c>
+      <c r="R10" s="2">
+        <v>84</v>
+      </c>
+      <c r="S10" s="2">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="T10" s="2">
+        <v>52</v>
+      </c>
+      <c r="U10" s="2">
+        <v>163</v>
+      </c>
+      <c r="V10" s="2">
+        <v>215</v>
+      </c>
+      <c r="W10" s="2">
+        <v>65</v>
+      </c>
+      <c r="X10" s="2">
+        <v>31</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>12</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>54</v>
+      </c>
+      <c r="AA10" s="2">
+        <v>95</v>
+      </c>
+      <c r="AB10" s="2">
+        <v>446</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="2"/>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="2">
+        <v>22</v>
+      </c>
+      <c r="D11" s="2">
+        <v>30</v>
+      </c>
+      <c r="E11" s="2">
+        <v>30</v>
+      </c>
+      <c r="F11" s="2">
+        <v>898</v>
+      </c>
+      <c r="G11" s="2">
+        <v>190</v>
+      </c>
+      <c r="H11" s="2">
+        <v>413</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0.46</v>
+      </c>
+      <c r="J11" s="2">
+        <v>63</v>
+      </c>
+      <c r="K11" s="2">
+        <v>154</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="M11" s="2">
+        <v>127</v>
+      </c>
+      <c r="N11" s="2">
+        <v>259</v>
+      </c>
+      <c r="O11" s="2">
+        <v>0.49</v>
+      </c>
+      <c r="P11" s="2">
+        <v>0.53600000000000003</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>85</v>
+      </c>
+      <c r="R11" s="2">
+        <v>116</v>
+      </c>
+      <c r="S11" s="2">
+        <v>0.73299999999999998</v>
+      </c>
+      <c r="T11" s="2">
+        <v>40</v>
+      </c>
+      <c r="U11" s="2">
+        <v>84</v>
+      </c>
+      <c r="V11" s="2">
+        <v>124</v>
+      </c>
+      <c r="W11" s="2">
+        <v>119</v>
+      </c>
+      <c r="X11" s="2">
+        <v>28</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>11</v>
+      </c>
+      <c r="Z11" s="2">
+        <v>89</v>
+      </c>
+      <c r="AA11" s="2">
+        <v>67</v>
+      </c>
+      <c r="AB11" s="2">
+        <v>528</v>
+      </c>
+      <c r="AC11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="2"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="2">
+        <v>24</v>
+      </c>
+      <c r="D12" s="2">
+        <v>57</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>811</v>
+      </c>
+      <c r="G12" s="2">
+        <v>137</v>
+      </c>
+      <c r="H12" s="2">
+        <v>296</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0.46300000000000002</v>
+      </c>
+      <c r="J12" s="2">
+        <v>58</v>
+      </c>
+      <c r="K12" s="2">
+        <v>152</v>
+      </c>
+      <c r="L12" s="2">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="M12" s="2">
+        <v>79</v>
+      </c>
+      <c r="N12" s="2">
+        <v>144</v>
+      </c>
+      <c r="O12" s="2">
+        <v>0.54900000000000004</v>
+      </c>
+      <c r="P12" s="2">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>43</v>
+      </c>
+      <c r="R12" s="2">
+        <v>51</v>
+      </c>
+      <c r="S12" s="2">
+        <v>0.84299999999999997</v>
+      </c>
+      <c r="T12" s="2">
+        <v>18</v>
+      </c>
+      <c r="U12" s="2">
+        <v>51</v>
+      </c>
+      <c r="V12" s="2">
+        <v>69</v>
+      </c>
+      <c r="W12" s="2">
+        <v>133</v>
+      </c>
+      <c r="X12" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y12" s="2">
+        <v>4</v>
+      </c>
+      <c r="Z12" s="2">
+        <v>54</v>
+      </c>
+      <c r="AA12" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB12" s="2">
+        <v>375</v>
+      </c>
+      <c r="AC12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="2"/>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="2">
+        <v>31</v>
+      </c>
+      <c r="D13" s="2">
+        <v>28</v>
+      </c>
+      <c r="E13" s="2">
+        <v>8</v>
+      </c>
+      <c r="F13" s="2">
+        <v>705</v>
+      </c>
+      <c r="G13" s="2">
+        <v>95</v>
+      </c>
+      <c r="H13" s="2">
+        <v>251</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0.378</v>
+      </c>
+      <c r="J13" s="2">
+        <v>32</v>
+      </c>
+      <c r="K13" s="2">
+        <v>106</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0.30199999999999999</v>
+      </c>
+      <c r="M13" s="2">
+        <v>63</v>
+      </c>
+      <c r="N13" s="2">
+        <v>145</v>
+      </c>
+      <c r="O13" s="2">
+        <v>0.434</v>
+      </c>
+      <c r="P13" s="2">
+        <v>0.442</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>80</v>
+      </c>
+      <c r="R13" s="2">
+        <v>96</v>
+      </c>
+      <c r="S13" s="2">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="T13" s="2">
+        <v>13</v>
+      </c>
+      <c r="U13" s="2">
+        <v>61</v>
+      </c>
+      <c r="V13" s="2">
+        <v>74</v>
+      </c>
+      <c r="W13" s="2">
+        <v>147</v>
+      </c>
+      <c r="X13" s="2">
+        <v>15</v>
+      </c>
+      <c r="Y13" s="2">
+        <v>5</v>
+      </c>
+      <c r="Z13" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA13" s="2">
+        <v>57</v>
+      </c>
+      <c r="AB13" s="2">
+        <v>302</v>
+      </c>
+      <c r="AC13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="2"/>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="2">
+        <v>25</v>
+      </c>
+      <c r="D14" s="2">
+        <v>45</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>438</v>
+      </c>
+      <c r="G14" s="2">
+        <v>72</v>
+      </c>
+      <c r="H14" s="2">
+        <v>142</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="J14" s="2">
+        <v>8</v>
+      </c>
+      <c r="K14" s="2">
+        <v>28</v>
+      </c>
+      <c r="L14" s="2">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="M14" s="2">
+        <v>64</v>
+      </c>
+      <c r="N14" s="2">
+        <v>114</v>
+      </c>
+      <c r="O14" s="2">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="P14" s="2">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>32</v>
+      </c>
+      <c r="R14" s="2">
+        <v>42</v>
+      </c>
+      <c r="S14" s="2">
+        <v>0.76200000000000001</v>
+      </c>
+      <c r="T14" s="2">
+        <v>40</v>
+      </c>
+      <c r="U14" s="2">
+        <v>83</v>
+      </c>
+      <c r="V14" s="2">
+        <v>123</v>
+      </c>
+      <c r="W14" s="2">
+        <v>44</v>
+      </c>
+      <c r="X14" s="2">
+        <v>39</v>
+      </c>
+      <c r="Y14" s="2">
+        <v>25</v>
+      </c>
+      <c r="Z14" s="2">
+        <v>26</v>
+      </c>
+      <c r="AA14" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB14" s="2">
+        <v>184</v>
+      </c>
+      <c r="AC14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="2"/>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="2">
+        <v>23</v>
+      </c>
+      <c r="D15" s="2">
+        <v>20</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>219</v>
+      </c>
+      <c r="G15" s="2">
+        <v>23</v>
+      </c>
+      <c r="H15" s="2">
+        <v>50</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0.46</v>
+      </c>
+      <c r="J15" s="2">
+        <v>4</v>
+      </c>
+      <c r="K15" s="2">
+        <v>14</v>
+      </c>
+      <c r="L15" s="2">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="M15" s="2">
+        <v>19</v>
+      </c>
+      <c r="N15" s="2">
+        <v>36</v>
+      </c>
+      <c r="O15" s="2">
+        <v>0.52800000000000002</v>
+      </c>
+      <c r="P15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>13</v>
+      </c>
+      <c r="R15" s="2">
+        <v>14</v>
+      </c>
+      <c r="S15" s="2">
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="T15" s="2">
+        <v>11</v>
+      </c>
+      <c r="U15" s="2">
+        <v>33</v>
+      </c>
+      <c r="V15" s="2">
+        <v>44</v>
+      </c>
+      <c r="W15" s="2">
+        <v>23</v>
+      </c>
+      <c r="X15" s="2">
+        <v>10</v>
+      </c>
+      <c r="Y15" s="2">
+        <v>3</v>
+      </c>
+      <c r="Z15" s="2">
+        <v>9</v>
+      </c>
+      <c r="AA15" s="2">
+        <v>15</v>
+      </c>
+      <c r="AB15" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="2"/>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="2">
+        <v>27</v>
+      </c>
+      <c r="D16" s="2">
+        <v>14</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <v>123</v>
+      </c>
+      <c r="G16" s="2">
+        <v>16</v>
+      </c>
+      <c r="H16" s="2">
+        <v>44</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="J16" s="2">
+        <v>15</v>
+      </c>
+      <c r="K16" s="2">
+        <v>38</v>
+      </c>
+      <c r="L16" s="2">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="M16" s="2">
+        <v>1</v>
+      </c>
+      <c r="N16" s="2">
+        <v>6</v>
+      </c>
+      <c r="O16" s="2">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="P16" s="2">
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>0</v>
+      </c>
+      <c r="R16" s="2">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2">
+        <v>4</v>
+      </c>
+      <c r="U16" s="2">
+        <v>10</v>
+      </c>
+      <c r="V16" s="2">
+        <v>14</v>
+      </c>
+      <c r="W16" s="2">
+        <v>10</v>
+      </c>
+      <c r="X16" s="2">
+        <v>5</v>
+      </c>
+      <c r="Y16" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="2">
+        <v>3</v>
+      </c>
+      <c r="AA16" s="2">
+        <v>7</v>
+      </c>
+      <c r="AB16" s="2">
+        <v>47</v>
+      </c>
+      <c r="AC16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="2"/>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="2">
+        <v>21</v>
+      </c>
+      <c r="D17" s="2">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <v>42</v>
+      </c>
+      <c r="G17" s="2">
+        <v>6</v>
+      </c>
+      <c r="H17" s="2">
+        <v>10</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="J17" s="2">
+        <v>2</v>
+      </c>
+      <c r="K17" s="2">
+        <v>5</v>
+      </c>
+      <c r="L17" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="M17" s="2">
+        <v>4</v>
+      </c>
+      <c r="N17" s="2">
+        <v>5</v>
+      </c>
+      <c r="O17" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="P17" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>1</v>
+      </c>
+      <c r="R17" s="2">
+        <v>2</v>
+      </c>
+      <c r="S17" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="T17" s="2">
+        <v>1</v>
+      </c>
+      <c r="U17" s="2">
+        <v>6</v>
+      </c>
+      <c r="V17" s="2">
+        <v>7</v>
+      </c>
+      <c r="W17" s="2">
+        <v>7</v>
+      </c>
+      <c r="X17" s="2">
+        <v>2</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>8</v>
+      </c>
+      <c r="AB17" s="2">
+        <v>15</v>
+      </c>
+      <c r="AC17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="2"/>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="2">
+        <v>23</v>
+      </c>
+      <c r="D18" s="2">
+        <v>7</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <v>23</v>
+      </c>
+      <c r="G18" s="2">
+        <v>3</v>
+      </c>
+      <c r="H18" s="2">
+        <v>10</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="J18" s="2">
+        <v>1</v>
+      </c>
+      <c r="K18" s="2">
+        <v>7</v>
+      </c>
+      <c r="L18" s="2">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="M18" s="2">
+        <v>2</v>
+      </c>
+      <c r="N18" s="2">
+        <v>3</v>
+      </c>
+      <c r="O18" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="P18" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>0</v>
+      </c>
+      <c r="R18" s="2">
+        <v>2</v>
+      </c>
+      <c r="S18" s="2">
+        <v>0</v>
+      </c>
+      <c r="T18" s="2">
+        <v>0</v>
+      </c>
+      <c r="U18" s="2">
+        <v>2</v>
+      </c>
+      <c r="V18" s="2">
+        <v>2</v>
+      </c>
+      <c r="W18" s="2">
+        <v>3</v>
+      </c>
+      <c r="X18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="2">
+        <v>2</v>
+      </c>
+      <c r="AB18" s="2">
+        <v>7</v>
+      </c>
+      <c r="AC18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="2"/>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="2">
+        <v>24</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2">
+        <v>22</v>
+      </c>
+      <c r="G19" s="2">
+        <v>6</v>
+      </c>
+      <c r="H19" s="2">
+        <v>9</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2">
+        <v>6</v>
+      </c>
+      <c r="N19" s="2">
+        <v>9</v>
+      </c>
+      <c r="O19" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="P19" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>2</v>
+      </c>
+      <c r="R19" s="2">
+        <v>3</v>
+      </c>
+      <c r="S19" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="T19" s="2">
+        <v>4</v>
+      </c>
+      <c r="U19" s="2">
+        <v>4</v>
+      </c>
+      <c r="V19" s="2">
+        <v>8</v>
+      </c>
+      <c r="W19" s="2">
+        <v>0</v>
+      </c>
+      <c r="X19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="2">
+        <v>2</v>
+      </c>
+      <c r="AA19" s="2">
+        <v>3</v>
+      </c>
+      <c r="AB19" s="2">
+        <v>14</v>
+      </c>
+      <c r="AC19" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="2"/>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="2">
+        <v>24</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
+        <v>17</v>
+      </c>
+      <c r="G20" s="2">
+        <v>1</v>
+      </c>
+      <c r="H20" s="2">
+        <v>8</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0</v>
+      </c>
+      <c r="K20" s="2">
+        <v>6</v>
+      </c>
+      <c r="L20" s="2">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2">
+        <v>1</v>
+      </c>
+      <c r="N20" s="2">
+        <v>2</v>
+      </c>
+      <c r="O20" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="P20" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>2</v>
+      </c>
+      <c r="R20" s="2">
+        <v>2</v>
+      </c>
+      <c r="S20" s="2">
+        <v>1</v>
+      </c>
+      <c r="T20" s="2">
+        <v>4</v>
+      </c>
+      <c r="U20" s="2">
+        <v>3</v>
+      </c>
+      <c r="V20" s="2">
+        <v>7</v>
+      </c>
+      <c r="W20" s="2">
+        <v>2</v>
+      </c>
+      <c r="X20" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="2">
+        <v>4</v>
+      </c>
+      <c r="AC20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="2"/>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="2">
+        <v>25</v>
+      </c>
+      <c r="D21" s="2">
+        <v>2</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2">
+        <v>13</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2">
+        <v>5</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2">
+        <v>5</v>
+      </c>
+      <c r="L21" s="2">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2">
+        <v>0</v>
+      </c>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>0</v>
+      </c>
+      <c r="R21" s="2">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2">
+        <v>0</v>
+      </c>
+      <c r="U21" s="2">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2">
+        <v>2</v>
+      </c>
+      <c r="W21" s="2">
+        <v>1</v>
+      </c>
+      <c r="X21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="2"/>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="2">
+        <v>25</v>
+      </c>
+      <c r="D22" s="2">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2">
+        <v>4</v>
+      </c>
+      <c r="G22" s="2">
+        <v>2</v>
+      </c>
+      <c r="H22" s="2">
+        <v>2</v>
+      </c>
+      <c r="I22" s="2">
+        <v>1</v>
+      </c>
+      <c r="J22" s="2">
+        <v>1</v>
+      </c>
+      <c r="K22" s="2">
+        <v>1</v>
+      </c>
+      <c r="L22" s="2">
+        <v>1</v>
+      </c>
+      <c r="M22" s="2">
+        <v>1</v>
+      </c>
+      <c r="N22" s="2">
+        <v>1</v>
+      </c>
+      <c r="O22" s="2">
+        <v>1</v>
+      </c>
+      <c r="P22" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>0</v>
+      </c>
+      <c r="R22" s="2">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2">
+        <v>0</v>
+      </c>
+      <c r="U22" s="2">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2">
+        <v>0</v>
+      </c>
+      <c r="W22" s="2">
+        <v>1</v>
+      </c>
+      <c r="X22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="2">
+        <v>5</v>
+      </c>
+      <c r="AC22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="2"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="https://www.basketball-reference.com/players/c/cunnica01.html" xr:uid="{EF23D96C-2BEC-6045-9431-FF503C9C8012}"/>
+    <hyperlink ref="B3" r:id="rId2" display="https://www.basketball-reference.com/players/h/harrito02.html" xr:uid="{CA24EA07-D7E7-4346-A684-64DAFC9F1C6D}"/>
+    <hyperlink ref="B4" r:id="rId3" display="https://www.basketball-reference.com/players/b/beaslma01.html" xr:uid="{6F32A0A7-D18E-FA40-8C57-FCADAFA09442}"/>
+    <hyperlink ref="AD4" r:id="rId4" location="all_smoy" display="https://www.basketball-reference.com/awards/awards_2025.html - all_smoy" xr:uid="{B1B015B0-2FE1-0F41-ACC3-C77EF6139C78}"/>
+    <hyperlink ref="B5" r:id="rId5" display="https://www.basketball-reference.com/players/h/hardati02.html" xr:uid="{1B29331C-8F1E-F045-B007-754D119C3563}"/>
+    <hyperlink ref="B6" r:id="rId6" display="https://www.basketball-reference.com/players/d/durenja01.html" xr:uid="{FBE87229-670B-A542-97AD-D7AD7E6FA582}"/>
+    <hyperlink ref="B7" r:id="rId7" display="https://www.basketball-reference.com/players/s/stewais01.html" xr:uid="{3791D041-6AEA-4249-BEC0-56E8AA6CDDFA}"/>
+    <hyperlink ref="B8" r:id="rId8" display="https://www.basketball-reference.com/players/t/thompau01.html" xr:uid="{3063C3A0-092D-684C-A616-C5DA2C5ACCDE}"/>
+    <hyperlink ref="B9" r:id="rId9" display="https://www.basketball-reference.com/players/h/hollaro01.html" xr:uid="{E0997C49-D78E-474E-B540-8EF242A6D45B}"/>
+    <hyperlink ref="B10" r:id="rId10" display="https://www.basketball-reference.com/players/f/fontesi01.html" xr:uid="{C43C9876-A0B4-0E49-8AD7-4D862027FDEC}"/>
+    <hyperlink ref="B11" r:id="rId11" display="https://www.basketball-reference.com/players/i/iveyja01.html" xr:uid="{5DDD6798-5999-684F-BF30-C0A20B01ABF8}"/>
+    <hyperlink ref="B12" r:id="rId12" display="https://www.basketball-reference.com/players/s/sassema01.html" xr:uid="{556B5B39-DBE0-9E42-BBDB-6A353CE9DA7B}"/>
+    <hyperlink ref="B13" r:id="rId13" display="https://www.basketball-reference.com/players/s/schrode01.html" xr:uid="{6FF27FE5-A55A-B344-85FF-3A8FD68E067F}"/>
+    <hyperlink ref="B14" r:id="rId14" display="https://www.basketball-reference.com/players/r/reedpa01.html" xr:uid="{3A140035-7FEB-E74A-B3AA-563AD20A226F}"/>
+    <hyperlink ref="B15" r:id="rId15" display="https://www.basketball-reference.com/players/m/moorewe01.html" xr:uid="{777C58C2-B132-A64B-8183-ABC4568E656C}"/>
+    <hyperlink ref="B16" r:id="rId16" display="https://www.basketball-reference.com/players/w/waterli01.html" xr:uid="{BA758B24-DDBF-0E4A-923C-79D9FBF2D777}"/>
+    <hyperlink ref="B17" r:id="rId17" display="https://www.basketball-reference.com/players/k/klintbo01.html" xr:uid="{C7EDB8DC-D1AF-4848-9611-01505F939AE8}"/>
+    <hyperlink ref="B18" r:id="rId18" display="https://www.basketball-reference.com/players/j/jenkida01.html" xr:uid="{3B4EAE8F-15DB-C94E-B231-367401EB9DBB}"/>
+    <hyperlink ref="B19" r:id="rId19" display="https://www.basketball-reference.com/players/s/smithto05.html" xr:uid="{5DED2542-8A62-C84E-BDA5-D575EA7DDDCB}"/>
+    <hyperlink ref="B20" r:id="rId20" display="https://www.basketball-reference.com/players/h/harpero02.html" xr:uid="{80652C05-ABD1-7E43-BB33-9A364D7445E1}"/>
+    <hyperlink ref="B21" r:id="rId21" display="https://www.basketball-reference.com/players/s/swideco01.html" xr:uid="{01C37520-4069-324D-9A86-78E67410A10F}"/>
+    <hyperlink ref="B22" r:id="rId22" display="https://www.basketball-reference.com/players/w/willial06.html" xr:uid="{11901D5C-39E9-1444-BD01-128A6E2A6486}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1E8E1F7-F7D8-FF44-A9B9-DF76A9B41396}">
+  <dimension ref="A1:AD22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2">
+        <v>70</v>
+      </c>
+      <c r="F2" s="2">
+        <v>70</v>
+      </c>
+      <c r="G2" s="2">
+        <v>2452</v>
+      </c>
+      <c r="H2" s="2">
+        <v>10</v>
+      </c>
+      <c r="I2" s="2">
+        <v>21.4</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="K2" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="L2" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="M2" s="2">
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="N2" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="O2" s="2">
+        <v>15.3</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>0.52100000000000002</v>
+      </c>
+      <c r="R2" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="S2" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="T2" s="2">
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="U2" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="V2" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="W2" s="2">
+        <v>6.2</v>
+      </c>
+      <c r="X2" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>26.9</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2">
+        <v>32</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="2">
+        <v>73</v>
+      </c>
+      <c r="F3" s="2">
+        <v>73</v>
+      </c>
+      <c r="G3" s="2">
+        <v>2305</v>
+      </c>
+      <c r="H3" s="2">
+        <v>6</v>
+      </c>
+      <c r="I3" s="2">
+        <v>12.6</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.47699999999999998</v>
+      </c>
+      <c r="K3" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="L3" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="N3" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="O3" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="R3" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="S3" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="T3" s="2">
+        <v>0.86099999999999999</v>
+      </c>
+      <c r="U3" s="2">
+        <v>1</v>
+      </c>
+      <c r="V3" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="W3" s="2">
+        <v>6.7</v>
+      </c>
+      <c r="X3" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="Y3" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="AA3" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>15.6</v>
+      </c>
+      <c r="AD3" s="2"/>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2">
+        <v>28</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="8">
+        <v>82</v>
+      </c>
+      <c r="F4" s="2">
+        <v>18</v>
+      </c>
+      <c r="G4" s="2">
+        <v>2283</v>
+      </c>
+      <c r="H4" s="2">
+        <v>7.3</v>
+      </c>
+      <c r="I4" s="2">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.43</v>
+      </c>
+      <c r="K4" s="2">
+        <v>5</v>
+      </c>
+      <c r="L4" s="2">
+        <v>12.1</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="N4" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="O4" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0.57899999999999996</v>
+      </c>
+      <c r="R4" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="S4" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="T4" s="2">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="U4" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="V4" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="W4" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="X4" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="AA4" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>2</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>21.1</v>
+      </c>
+      <c r="AD4" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2">
+        <v>32</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2">
+        <v>77</v>
+      </c>
+      <c r="F5" s="2">
+        <v>77</v>
+      </c>
+      <c r="G5" s="2">
+        <v>2153</v>
+      </c>
+      <c r="H5" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I5" s="2">
+        <v>11.4</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.40600000000000003</v>
+      </c>
+      <c r="K5" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="L5" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0.36799999999999999</v>
+      </c>
+      <c r="N5" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="O5" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0.48399999999999999</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="R5" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="S5" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="T5" s="2">
+        <v>0.85499999999999998</v>
+      </c>
+      <c r="U5" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="V5" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="W5" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="X5" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="Y5" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="AA5" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="AB5" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="AC5" s="2">
+        <v>14.1</v>
+      </c>
+      <c r="AD5" s="2"/>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2">
+        <v>21</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2">
+        <v>78</v>
+      </c>
+      <c r="F6" s="2">
+        <v>78</v>
+      </c>
+      <c r="G6" s="2">
+        <v>2034</v>
+      </c>
+      <c r="H6" s="2">
+        <v>6.7</v>
+      </c>
+      <c r="I6" s="2">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2">
+        <v>6.7</v>
+      </c>
+      <c r="O6" s="2">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="R6" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="S6" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="T6" s="2">
+        <v>0.66900000000000004</v>
+      </c>
+      <c r="U6" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="V6" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="W6" s="2">
+        <v>14.3</v>
+      </c>
+      <c r="X6" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="Y6" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="AB6" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AC6" s="2">
+        <v>16.2</v>
+      </c>
+      <c r="AD6" s="2"/>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="2">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2">
+        <v>72</v>
+      </c>
+      <c r="F7" s="2">
+        <v>4</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1434</v>
+      </c>
+      <c r="H7" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.55900000000000005</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="N7" s="2">
+        <v>4</v>
+      </c>
+      <c r="O7" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0.60699999999999998</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0.58599999999999997</v>
+      </c>
+      <c r="R7" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="S7" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="T7" s="2">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="U7" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="V7" s="2">
+        <v>6.8</v>
+      </c>
+      <c r="W7" s="2">
+        <v>10</v>
+      </c>
+      <c r="X7" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="AB7" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>10.9</v>
+      </c>
+      <c r="AD7" s="2"/>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="2">
+        <v>22</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2">
+        <v>59</v>
+      </c>
+      <c r="F8" s="2">
+        <v>48</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1328</v>
+      </c>
+      <c r="H8" s="2">
+        <v>6.7</v>
+      </c>
+      <c r="I8" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="M8" s="2">
+        <v>0.224</v>
+      </c>
+      <c r="N8" s="2">
+        <v>6.4</v>
+      </c>
+      <c r="O8" s="2">
+        <v>11.1</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0.57199999999999995</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="R8" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="S8" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="T8" s="2">
+        <v>0.64100000000000001</v>
+      </c>
+      <c r="U8" s="2">
+        <v>3</v>
+      </c>
+      <c r="V8" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="W8" s="2">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="X8" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AB8" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="AD8" s="2"/>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="2">
+        <v>19</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="2">
+        <v>81</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1266</v>
+      </c>
+      <c r="H9" s="2">
+        <v>5.6</v>
+      </c>
+      <c r="I9" s="2">
+        <v>11.8</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="K9" s="2">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="N9" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="O9" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="P9" s="2">
+        <v>0.60799999999999998</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>0.51700000000000002</v>
+      </c>
+      <c r="R9" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="S9" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="T9" s="2">
+        <v>0.754</v>
+      </c>
+      <c r="U9" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="V9" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="W9" s="2">
+        <v>6.2</v>
+      </c>
+      <c r="X9" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>2</v>
+      </c>
+      <c r="AB9" s="2">
+        <v>4</v>
+      </c>
+      <c r="AC9" s="2">
+        <v>14.8</v>
+      </c>
+      <c r="AD9" s="2"/>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="2">
+        <v>29</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="2">
+        <v>75</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1237</v>
+      </c>
+      <c r="H10" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="I10" s="2">
+        <v>10.9</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.40200000000000002</v>
+      </c>
+      <c r="K10" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="L10" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="N10" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="O10" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="P10" s="2">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>0.504</v>
+      </c>
+      <c r="R10" s="2">
+        <v>2</v>
+      </c>
+      <c r="S10" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="T10" s="2">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="U10" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="V10" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="W10" s="2">
+        <v>6.3</v>
+      </c>
+      <c r="X10" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="AA10" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="AB10" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>13</v>
+      </c>
+      <c r="AD10" s="2"/>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="2">
+        <v>22</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2">
+        <v>30</v>
+      </c>
+      <c r="F11" s="2">
+        <v>30</v>
+      </c>
+      <c r="G11" s="2">
+        <v>898</v>
+      </c>
+      <c r="H11" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="I11" s="2">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.46</v>
+      </c>
+      <c r="K11" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="L11" s="2">
+        <v>6.2</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="N11" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="O11" s="2">
+        <v>10.4</v>
+      </c>
+      <c r="P11" s="2">
+        <v>0.49</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>0.53600000000000003</v>
+      </c>
+      <c r="R11" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="S11" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="T11" s="2">
+        <v>0.73299999999999998</v>
+      </c>
+      <c r="U11" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="V11" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="W11" s="2">
+        <v>5</v>
+      </c>
+      <c r="X11" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="Z11" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="AA11" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="AB11" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="AC11" s="2">
+        <v>21.2</v>
+      </c>
+      <c r="AD11" s="2"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="2">
+        <v>24</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2">
+        <v>57</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2">
+        <v>811</v>
+      </c>
+      <c r="H12" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="I12" s="2">
+        <v>13.1</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0.46300000000000002</v>
+      </c>
+      <c r="K12" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="L12" s="2">
+        <v>6.7</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="N12" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="O12" s="2">
+        <v>6.4</v>
+      </c>
+      <c r="P12" s="2">
+        <v>0.54900000000000004</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="R12" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="S12" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="T12" s="2">
+        <v>0.84299999999999997</v>
+      </c>
+      <c r="U12" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="V12" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="W12" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="X12" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="Y12" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="Z12" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA12" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="AB12" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="AC12" s="2">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="AD12" s="2"/>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="2">
+        <v>31</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2">
+        <v>28</v>
+      </c>
+      <c r="F13" s="2">
+        <v>8</v>
+      </c>
+      <c r="G13" s="2">
+        <v>705</v>
+      </c>
+      <c r="H13" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="I13" s="2">
+        <v>12.8</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0.378</v>
+      </c>
+      <c r="K13" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="L13" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0.30199999999999999</v>
+      </c>
+      <c r="N13" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="O13" s="2">
+        <v>7.4</v>
+      </c>
+      <c r="P13" s="2">
+        <v>0.434</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>0.442</v>
+      </c>
+      <c r="R13" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="S13" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="T13" s="2">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="U13" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="V13" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="W13" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="X13" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="Y13" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="Z13" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="AA13" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="AB13" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="AC13" s="2">
+        <v>15.4</v>
+      </c>
+      <c r="AD13" s="2"/>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="2">
+        <v>25</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="2">
+        <v>45</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>438</v>
+      </c>
+      <c r="H14" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="I14" s="2">
+        <v>11.7</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="K14" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="L14" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M14" s="2">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="N14" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="O14" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="P14" s="2">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="R14" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="S14" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="T14" s="2">
+        <v>0.76200000000000001</v>
+      </c>
+      <c r="U14" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="V14" s="2">
+        <v>6.8</v>
+      </c>
+      <c r="W14" s="2">
+        <v>10.1</v>
+      </c>
+      <c r="X14" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="Y14" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="Z14" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="AA14" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="AB14" s="2">
+        <v>6.2</v>
+      </c>
+      <c r="AC14" s="2">
+        <v>15.1</v>
+      </c>
+      <c r="AD14" s="2"/>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="2">
+        <v>23</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="2">
+        <v>20</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>219</v>
+      </c>
+      <c r="H15" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="I15" s="2">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0.46</v>
+      </c>
+      <c r="K15" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="L15" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M15" s="2">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="N15" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="O15" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="P15" s="2">
+        <v>0.52800000000000002</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="R15" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="S15" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="T15" s="2">
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="U15" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="V15" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="W15" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="X15" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="Y15" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="Z15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AA15" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="AB15" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="AC15" s="2">
+        <v>10.4</v>
+      </c>
+      <c r="AD15" s="2"/>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="2">
+        <v>27</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="2">
+        <v>14</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
+        <v>123</v>
+      </c>
+      <c r="H16" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="I16" s="2">
+        <v>12.9</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="K16" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L16" s="2">
+        <v>11.1</v>
+      </c>
+      <c r="M16" s="2">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="N16" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="O16" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="P16" s="2">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="R16" s="2">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2">
+        <v>0</v>
+      </c>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="V16" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="W16" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="X16" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="Y16" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="Z16" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="AA16" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="AB16" s="2">
+        <v>2</v>
+      </c>
+      <c r="AC16" s="2">
+        <v>13.8</v>
+      </c>
+      <c r="AD16" s="2"/>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="2">
+        <v>21</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="2">
+        <v>8</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
+        <v>42</v>
+      </c>
+      <c r="H17" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="I17" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="K17" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="L17" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="M17" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="N17" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="O17" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="P17" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="R17" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="S17" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="T17" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="U17" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="V17" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="W17" s="2">
+        <v>6</v>
+      </c>
+      <c r="X17" s="2">
+        <v>6</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="Z17" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="AB17" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="AC17" s="2">
+        <v>12.9</v>
+      </c>
+      <c r="AD17" s="2"/>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="2">
+        <v>23</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="2">
+        <v>7</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
+        <v>23</v>
+      </c>
+      <c r="H18" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="I18" s="2">
+        <v>15.7</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="L18" s="2">
+        <v>11</v>
+      </c>
+      <c r="M18" s="2">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="N18" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="O18" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="P18" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="R18" s="2">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="T18" s="2">
+        <v>0</v>
+      </c>
+      <c r="U18" s="2">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="W18" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="X18" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="Y18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="AB18" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="AC18" s="2">
+        <v>11</v>
+      </c>
+      <c r="AD18" s="2"/>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="2">
+        <v>24</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2">
+        <v>22</v>
+      </c>
+      <c r="H19" s="2">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="I19" s="2">
+        <v>14.7</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="K19" s="2">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="O19" s="2">
+        <v>14.7</v>
+      </c>
+      <c r="P19" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="R19" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="S19" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="T19" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="U19" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="V19" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="W19" s="2">
+        <v>13.1</v>
+      </c>
+      <c r="X19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="AB19" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="AC19" s="2">
+        <v>22.9</v>
+      </c>
+      <c r="AD19" s="2"/>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="2">
+        <v>24</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2">
+        <v>17</v>
+      </c>
+      <c r="H20" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="I20" s="2">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="K20" s="2">
+        <v>0</v>
+      </c>
+      <c r="L20" s="2">
+        <v>12.7</v>
+      </c>
+      <c r="M20" s="2">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="O20" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="P20" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="R20" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="S20" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="T20" s="2">
+        <v>1</v>
+      </c>
+      <c r="U20" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="V20" s="2">
+        <v>6.4</v>
+      </c>
+      <c r="W20" s="2">
+        <v>14.8</v>
+      </c>
+      <c r="X20" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="Y20" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="AD20" s="2"/>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="2">
+        <v>25</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="2">
+        <v>2</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
+        <v>13</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>13.8</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2">
+        <v>13.8</v>
+      </c>
+      <c r="M21" s="2">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2">
+        <v>0</v>
+      </c>
+      <c r="O21" s="2">
+        <v>0</v>
+      </c>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2">
+        <v>0</v>
+      </c>
+      <c r="R21" s="2">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2">
+        <v>0</v>
+      </c>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="W21" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="X21" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="Y21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="AC21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="2"/>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="2">
+        <v>25</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2">
+        <v>4</v>
+      </c>
+      <c r="H22" s="2">
+        <v>18</v>
+      </c>
+      <c r="I22" s="2">
+        <v>18</v>
+      </c>
+      <c r="J22" s="2">
+        <v>1</v>
+      </c>
+      <c r="K22" s="2">
+        <v>9</v>
+      </c>
+      <c r="L22" s="2">
+        <v>9</v>
+      </c>
+      <c r="M22" s="2">
+        <v>1</v>
+      </c>
+      <c r="N22" s="2">
+        <v>9</v>
+      </c>
+      <c r="O22" s="2">
+        <v>9</v>
+      </c>
+      <c r="P22" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="R22" s="2">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2">
+        <v>0</v>
+      </c>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2">
+        <v>0</v>
+      </c>
+      <c r="W22" s="2">
+        <v>0</v>
+      </c>
+      <c r="X22" s="2">
+        <v>9</v>
+      </c>
+      <c r="Y22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="2">
+        <v>45</v>
+      </c>
+      <c r="AD22" s="2"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="https://www.basketball-reference.com/players/c/cunnica01.html" xr:uid="{B1B68958-4FFD-2D49-86C8-C1963EE9FDF6}"/>
+    <hyperlink ref="B3" r:id="rId2" display="https://www.basketball-reference.com/players/h/harrito02.html" xr:uid="{C9308582-8F6B-D648-A098-6A3778D1FF22}"/>
+    <hyperlink ref="B4" r:id="rId3" display="https://www.basketball-reference.com/players/b/beaslma01.html" xr:uid="{C8EAF7BB-592B-B14E-A5E6-56467202622E}"/>
+    <hyperlink ref="AD4" r:id="rId4" location="all_smoy" display="https://www.basketball-reference.com/awards/awards_2025.html - all_smoy" xr:uid="{3682D4DF-C03E-F44A-B09A-D0DFF149BC98}"/>
+    <hyperlink ref="B5" r:id="rId5" display="https://www.basketball-reference.com/players/h/hardati02.html" xr:uid="{7A0D3E9E-CF34-A94E-9FD0-1F3AEAFD325A}"/>
+    <hyperlink ref="B6" r:id="rId6" display="https://www.basketball-reference.com/players/d/durenja01.html" xr:uid="{5C81C123-5995-5C41-BE1E-0062EAEB8737}"/>
+    <hyperlink ref="B7" r:id="rId7" display="https://www.basketball-reference.com/players/s/stewais01.html" xr:uid="{18710BE7-F529-CE44-A26C-9F396667EF3E}"/>
+    <hyperlink ref="B8" r:id="rId8" display="https://www.basketball-reference.com/players/t/thompau01.html" xr:uid="{4A96AB58-242D-9D4D-8272-02CFF178DE31}"/>
+    <hyperlink ref="B9" r:id="rId9" display="https://www.basketball-reference.com/players/h/hollaro01.html" xr:uid="{D04F78F2-3DBB-B741-AA76-B0B98C7BCBFB}"/>
+    <hyperlink ref="B10" r:id="rId10" display="https://www.basketball-reference.com/players/f/fontesi01.html" xr:uid="{B3AF1CEE-DC8B-A647-B0E8-8BAC4C6F183A}"/>
+    <hyperlink ref="B11" r:id="rId11" display="https://www.basketball-reference.com/players/i/iveyja01.html" xr:uid="{865EBC86-E83A-6C48-9C41-8E280645AB87}"/>
+    <hyperlink ref="B12" r:id="rId12" display="https://www.basketball-reference.com/players/s/sassema01.html" xr:uid="{92FEEA26-EB99-5B4E-858D-C0035E1B0CF7}"/>
+    <hyperlink ref="B13" r:id="rId13" display="https://www.basketball-reference.com/players/s/schrode01.html" xr:uid="{E1176FB5-D241-1549-B707-72CD420F5175}"/>
+    <hyperlink ref="B14" r:id="rId14" display="https://www.basketball-reference.com/players/r/reedpa01.html" xr:uid="{CEFD44EF-1E6F-B145-AB16-6F4ADB50A046}"/>
+    <hyperlink ref="B15" r:id="rId15" display="https://www.basketball-reference.com/players/m/moorewe01.html" xr:uid="{C6D1A63E-3A12-864C-B5C6-EB817C00E000}"/>
+    <hyperlink ref="B16" r:id="rId16" display="https://www.basketball-reference.com/players/w/waterli01.html" xr:uid="{69AF93CF-542E-D04F-A41D-910A600315AF}"/>
+    <hyperlink ref="B17" r:id="rId17" display="https://www.basketball-reference.com/players/k/klintbo01.html" xr:uid="{BA5C8BFF-8A80-A042-B867-6DA0C402FF9B}"/>
+    <hyperlink ref="B18" r:id="rId18" display="https://www.basketball-reference.com/players/j/jenkida01.html" xr:uid="{0FB19C54-D746-AC40-B03C-FBCAF2EDFEF4}"/>
+    <hyperlink ref="B19" r:id="rId19" display="https://www.basketball-reference.com/players/s/smithto05.html" xr:uid="{16228145-2392-E942-B1E9-66926C422641}"/>
+    <hyperlink ref="B20" r:id="rId20" display="https://www.basketball-reference.com/players/h/harpero02.html" xr:uid="{BC85AA9A-B9B6-564A-87E4-D5FB7BFA2650}"/>
+    <hyperlink ref="B21" r:id="rId21" display="https://www.basketball-reference.com/players/s/swideco01.html" xr:uid="{049F6377-B1C3-7C40-8645-D6C8DF116243}"/>
+    <hyperlink ref="B22" r:id="rId22" display="https://www.basketball-reference.com/players/w/willial06.html" xr:uid="{A1877D66-4660-CD47-9548-E40F8838DA6F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Projects/Pistons_Players_Data_2024-2025.xlsx
+++ b/Projects/Pistons_Players_Data_2024-2025.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EF60BEA-AF5A-B643-B0E6-5FFA61386524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E506376-CA1B-CC40-A2F2-540D5D9A1CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="580" yWindow="680" windowWidth="28040" windowHeight="17180" activeTab="3" xr2:uid="{9F5AD747-0CA0-0449-80A8-FFDBC90AA643}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17560" activeTab="6" xr2:uid="{9F5AD747-0CA0-0449-80A8-FFDBC90AA643}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
     <sheet name="Regular Season Averages" sheetId="2" r:id="rId2"/>
     <sheet name="Regular Season Totals" sheetId="3" r:id="rId3"/>
     <sheet name="Per 36 Minutes" sheetId="4" r:id="rId4"/>
+    <sheet name="Per 100 Poss" sheetId="5" r:id="rId5"/>
+    <sheet name="Advanced" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet6" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="108">
   <si>
     <t>No.</t>
   </si>
@@ -496,6 +499,72 @@
   <si>
     <t>Trp-Dbl</t>
   </si>
+  <si>
+    <t>ORtg</t>
+  </si>
+  <si>
+    <t>DRtg</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>TS%</t>
+  </si>
+  <si>
+    <t>3PAr</t>
+  </si>
+  <si>
+    <t>FTr</t>
+  </si>
+  <si>
+    <t>ORB%</t>
+  </si>
+  <si>
+    <t>DRB%</t>
+  </si>
+  <si>
+    <t>TRB%</t>
+  </si>
+  <si>
+    <t>AST%</t>
+  </si>
+  <si>
+    <t>STL%</t>
+  </si>
+  <si>
+    <t>BLK%</t>
+  </si>
+  <si>
+    <t>TOV%</t>
+  </si>
+  <si>
+    <t>USG%</t>
+  </si>
+  <si>
+    <t>OWS</t>
+  </si>
+  <si>
+    <t>DWS</t>
+  </si>
+  <si>
+    <t>WS</t>
+  </si>
+  <si>
+    <t>WS/48</t>
+  </si>
+  <si>
+    <t>OBPM</t>
+  </si>
+  <si>
+    <t>DBPM</t>
+  </si>
+  <si>
+    <t>BPM</t>
+  </si>
+  <si>
+    <t>VORP</t>
+  </si>
 </sst>
 </file>
 
@@ -7716,4 +7785,4028 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BE6117D-9A11-C541-9C37-6506A55E6BE4}">
+  <dimension ref="A1:AE22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2">
+        <v>70</v>
+      </c>
+      <c r="E2" s="2">
+        <v>70</v>
+      </c>
+      <c r="F2" s="2">
+        <v>2452</v>
+      </c>
+      <c r="G2" s="2">
+        <v>13.4</v>
+      </c>
+      <c r="H2" s="2">
+        <v>28.6</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="J2" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="K2" s="2">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="L2" s="2">
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="M2" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="N2" s="2">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0.52100000000000002</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="R2" s="2">
+        <v>7.3</v>
+      </c>
+      <c r="S2" s="2">
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="T2" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U2" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="V2" s="2">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="W2" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="X2" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>35.9</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>112</v>
+      </c>
+      <c r="AD2" s="2">
+        <v>113</v>
+      </c>
+      <c r="AE2" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2">
+        <v>32</v>
+      </c>
+      <c r="D3" s="2">
+        <v>73</v>
+      </c>
+      <c r="E3" s="2">
+        <v>73</v>
+      </c>
+      <c r="F3" s="2">
+        <v>2305</v>
+      </c>
+      <c r="G3" s="2">
+        <v>8</v>
+      </c>
+      <c r="H3" s="2">
+        <v>16.8</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0.47699999999999998</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="K3" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="L3" s="2">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="M3" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="N3" s="2">
+        <v>11.3</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>3</v>
+      </c>
+      <c r="R3" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="S3" s="2">
+        <v>0.86099999999999999</v>
+      </c>
+      <c r="T3" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="U3" s="2">
+        <v>7.7</v>
+      </c>
+      <c r="V3" s="2">
+        <v>9</v>
+      </c>
+      <c r="W3" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="X3" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="Y3" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="AA3" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>20.9</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>116</v>
+      </c>
+      <c r="AD3" s="2">
+        <v>113</v>
+      </c>
+      <c r="AE3" s="2"/>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2">
+        <v>28</v>
+      </c>
+      <c r="D4" s="8">
+        <v>82</v>
+      </c>
+      <c r="E4" s="2">
+        <v>18</v>
+      </c>
+      <c r="F4" s="2">
+        <v>2283</v>
+      </c>
+      <c r="G4" s="2">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="H4" s="2">
+        <v>22.6</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0.43</v>
+      </c>
+      <c r="J4" s="8">
+        <v>6.7</v>
+      </c>
+      <c r="K4" s="2">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="M4" s="2">
+        <v>3</v>
+      </c>
+      <c r="N4" s="2">
+        <v>6.4</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0.57899999999999996</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>2</v>
+      </c>
+      <c r="R4" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="S4" s="2">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="T4" s="2">
+        <v>1</v>
+      </c>
+      <c r="U4" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="V4" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="W4" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="X4" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="AA4" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>28.1</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>116</v>
+      </c>
+      <c r="AD4" s="2">
+        <v>117</v>
+      </c>
+      <c r="AE4" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2">
+        <v>32</v>
+      </c>
+      <c r="D5" s="2">
+        <v>77</v>
+      </c>
+      <c r="E5" s="2">
+        <v>77</v>
+      </c>
+      <c r="F5" s="2">
+        <v>2153</v>
+      </c>
+      <c r="G5" s="2">
+        <v>6.2</v>
+      </c>
+      <c r="H5" s="2">
+        <v>15.2</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.40600000000000003</v>
+      </c>
+      <c r="J5" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="K5" s="2">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="L5" s="2">
+        <v>0.36799999999999999</v>
+      </c>
+      <c r="M5" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="N5" s="2">
+        <v>5</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0.48399999999999999</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="R5" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="S5" s="2">
+        <v>0.85499999999999998</v>
+      </c>
+      <c r="T5" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="U5" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="V5" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="W5" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="X5" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="Y5" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AA5" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="AB5" s="2">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="AC5" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD5" s="2">
+        <v>118</v>
+      </c>
+      <c r="AE5" s="2"/>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2">
+        <v>21</v>
+      </c>
+      <c r="D6" s="2">
+        <v>78</v>
+      </c>
+      <c r="E6" s="2">
+        <v>78</v>
+      </c>
+      <c r="F6" s="2">
+        <v>2034</v>
+      </c>
+      <c r="G6" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="H6" s="2">
+        <v>12.9</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="N6" s="2">
+        <v>12.9</v>
+      </c>
+      <c r="O6" s="2">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="R6" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="S6" s="2">
+        <v>0.66900000000000004</v>
+      </c>
+      <c r="T6" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="U6" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="V6" s="2">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="W6" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X6" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="Y6" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="AB6" s="2">
+        <v>21.7</v>
+      </c>
+      <c r="AC6" s="2">
+        <v>134</v>
+      </c>
+      <c r="AD6" s="2">
+        <v>109</v>
+      </c>
+      <c r="AE6" s="2"/>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="2">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2">
+        <v>72</v>
+      </c>
+      <c r="E7" s="2">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1434</v>
+      </c>
+      <c r="G7" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="H7" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.55900000000000005</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="M7" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="N7" s="2">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="O7" s="2">
+        <v>0.60699999999999998</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0.58599999999999997</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="R7" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="S7" s="2">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="T7" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="U7" s="2">
+        <v>9</v>
+      </c>
+      <c r="V7" s="2">
+        <v>13.4</v>
+      </c>
+      <c r="W7" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="X7" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="AB7" s="2">
+        <v>14.6</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>125</v>
+      </c>
+      <c r="AD7" s="2">
+        <v>110</v>
+      </c>
+      <c r="AE7" s="2"/>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="2">
+        <v>22</v>
+      </c>
+      <c r="D8" s="2">
+        <v>59</v>
+      </c>
+      <c r="E8" s="2">
+        <v>48</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1328</v>
+      </c>
+      <c r="G8" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="H8" s="2">
+        <v>16.7</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0.224</v>
+      </c>
+      <c r="M8" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="N8" s="2">
+        <v>14.9</v>
+      </c>
+      <c r="O8" s="2">
+        <v>0.57199999999999995</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="R8" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="S8" s="2">
+        <v>0.64100000000000001</v>
+      </c>
+      <c r="T8" s="2">
+        <v>4</v>
+      </c>
+      <c r="U8" s="2">
+        <v>7</v>
+      </c>
+      <c r="V8" s="2">
+        <v>11</v>
+      </c>
+      <c r="W8" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X8" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="AB8" s="2">
+        <v>21.5</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>115</v>
+      </c>
+      <c r="AD8" s="2">
+        <v>108</v>
+      </c>
+      <c r="AE8" s="2"/>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="2">
+        <v>19</v>
+      </c>
+      <c r="D9" s="2">
+        <v>81</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1266</v>
+      </c>
+      <c r="G9" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="H9" s="2">
+        <v>15.8</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="K9" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="M9" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="N9" s="2">
+        <v>10.1</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0.60799999999999998</v>
+      </c>
+      <c r="P9" s="2">
+        <v>0.51700000000000002</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="R9" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="S9" s="2">
+        <v>0.754</v>
+      </c>
+      <c r="T9" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U9" s="2">
+        <v>6.8</v>
+      </c>
+      <c r="V9" s="2">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="W9" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="X9" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="AB9" s="2">
+        <v>19.8</v>
+      </c>
+      <c r="AC9" s="2">
+        <v>107</v>
+      </c>
+      <c r="AD9" s="2">
+        <v>113</v>
+      </c>
+      <c r="AE9" s="2"/>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="2">
+        <v>29</v>
+      </c>
+      <c r="D10" s="2">
+        <v>75</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1237</v>
+      </c>
+      <c r="G10" s="2">
+        <v>5.8</v>
+      </c>
+      <c r="H10" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0.40200000000000002</v>
+      </c>
+      <c r="J10" s="2">
+        <v>3</v>
+      </c>
+      <c r="K10" s="2">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="M10" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="N10" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="O10" s="2">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="P10" s="2">
+        <v>0.504</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="R10" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="S10" s="2">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="T10" s="2">
+        <v>2</v>
+      </c>
+      <c r="U10" s="2">
+        <v>6.3</v>
+      </c>
+      <c r="V10" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="W10" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="X10" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="AA10" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="AB10" s="2">
+        <v>17.3</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>109</v>
+      </c>
+      <c r="AD10" s="2">
+        <v>115</v>
+      </c>
+      <c r="AE10" s="2"/>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="2">
+        <v>22</v>
+      </c>
+      <c r="D11" s="2">
+        <v>30</v>
+      </c>
+      <c r="E11" s="2">
+        <v>30</v>
+      </c>
+      <c r="F11" s="2">
+        <v>898</v>
+      </c>
+      <c r="G11" s="2">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="H11" s="2">
+        <v>22.1</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0.46</v>
+      </c>
+      <c r="J11" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="K11" s="2">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="M11" s="2">
+        <v>6.8</v>
+      </c>
+      <c r="N11" s="2">
+        <v>13.9</v>
+      </c>
+      <c r="O11" s="2">
+        <v>0.49</v>
+      </c>
+      <c r="P11" s="2">
+        <v>0.53600000000000003</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="R11" s="2">
+        <v>6.2</v>
+      </c>
+      <c r="S11" s="2">
+        <v>0.73299999999999998</v>
+      </c>
+      <c r="T11" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="U11" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="V11" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="W11" s="2">
+        <v>6.4</v>
+      </c>
+      <c r="X11" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="Z11" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="AA11" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="AB11" s="2">
+        <v>28.3</v>
+      </c>
+      <c r="AC11" s="2">
+        <v>108</v>
+      </c>
+      <c r="AD11" s="2">
+        <v>115</v>
+      </c>
+      <c r="AE11" s="2"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="2">
+        <v>24</v>
+      </c>
+      <c r="D12" s="2">
+        <v>57</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>811</v>
+      </c>
+      <c r="G12" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="H12" s="2">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0.46300000000000002</v>
+      </c>
+      <c r="J12" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="K12" s="2">
+        <v>9</v>
+      </c>
+      <c r="L12" s="2">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="M12" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="N12" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="O12" s="2">
+        <v>0.54900000000000004</v>
+      </c>
+      <c r="P12" s="2">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="R12" s="2">
+        <v>3</v>
+      </c>
+      <c r="S12" s="2">
+        <v>0.84299999999999997</v>
+      </c>
+      <c r="T12" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U12" s="2">
+        <v>3</v>
+      </c>
+      <c r="V12" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="W12" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="X12" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Y12" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Z12" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="AA12" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="AB12" s="2">
+        <v>22.2</v>
+      </c>
+      <c r="AC12" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD12" s="2">
+        <v>115</v>
+      </c>
+      <c r="AE12" s="2"/>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="2">
+        <v>31</v>
+      </c>
+      <c r="D13" s="2">
+        <v>28</v>
+      </c>
+      <c r="E13" s="2">
+        <v>8</v>
+      </c>
+      <c r="F13" s="2">
+        <v>705</v>
+      </c>
+      <c r="G13" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="H13" s="2">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0.378</v>
+      </c>
+      <c r="J13" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="K13" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0.30199999999999999</v>
+      </c>
+      <c r="M13" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="N13" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="O13" s="2">
+        <v>0.434</v>
+      </c>
+      <c r="P13" s="2">
+        <v>0.442</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="R13" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="S13" s="2">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="T13" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="U13" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="V13" s="2">
+        <v>5</v>
+      </c>
+      <c r="W13" s="2">
+        <v>10</v>
+      </c>
+      <c r="X13" s="2">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="Z13" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="AA13" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="AB13" s="2">
+        <v>20.6</v>
+      </c>
+      <c r="AC13" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD13" s="2">
+        <v>117</v>
+      </c>
+      <c r="AE13" s="2"/>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="2">
+        <v>25</v>
+      </c>
+      <c r="D14" s="2">
+        <v>45</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>438</v>
+      </c>
+      <c r="G14" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="H14" s="2">
+        <v>15.6</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="K14" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="L14" s="2">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="M14" s="2">
+        <v>7</v>
+      </c>
+      <c r="N14" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="O14" s="2">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="P14" s="2">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="R14" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="S14" s="2">
+        <v>0.76200000000000001</v>
+      </c>
+      <c r="T14" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="U14" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="V14" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="W14" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="X14" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="Y14" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="Z14" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="AA14" s="2">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="AB14" s="2">
+        <v>20.2</v>
+      </c>
+      <c r="AC14" s="2">
+        <v>118</v>
+      </c>
+      <c r="AD14" s="2">
+        <v>103</v>
+      </c>
+      <c r="AE14" s="2"/>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="2">
+        <v>23</v>
+      </c>
+      <c r="D15" s="2">
+        <v>20</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>219</v>
+      </c>
+      <c r="G15" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H15" s="2">
+        <v>11</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0.46</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="K15" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="L15" s="2">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="M15" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="N15" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="O15" s="2">
+        <v>0.52800000000000002</v>
+      </c>
+      <c r="P15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="R15" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="S15" s="2">
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="T15" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="U15" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="V15" s="2">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="W15" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X15" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Y15" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="Z15" s="2">
+        <v>2</v>
+      </c>
+      <c r="AA15" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="AB15" s="2">
+        <v>13.8</v>
+      </c>
+      <c r="AC15" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD15" s="2">
+        <v>112</v>
+      </c>
+      <c r="AE15" s="2"/>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="2">
+        <v>27</v>
+      </c>
+      <c r="D16" s="2">
+        <v>14</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <v>123</v>
+      </c>
+      <c r="G16" s="2">
+        <v>6.3</v>
+      </c>
+      <c r="H16" s="2">
+        <v>17.2</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="J16" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="K16" s="2">
+        <v>14.9</v>
+      </c>
+      <c r="L16" s="2">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="M16" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="N16" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="O16" s="2">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="P16" s="2">
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>0</v>
+      </c>
+      <c r="R16" s="2">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="U16" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="V16" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="W16" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="X16" s="2">
+        <v>2</v>
+      </c>
+      <c r="Y16" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="Z16" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="AA16" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="AB16" s="2">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="AC16" s="2">
+        <v>115</v>
+      </c>
+      <c r="AD16" s="2">
+        <v>115</v>
+      </c>
+      <c r="AE16" s="2"/>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="2">
+        <v>21</v>
+      </c>
+      <c r="D17" s="2">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <v>42</v>
+      </c>
+      <c r="G17" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="H17" s="2">
+        <v>11.4</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="J17" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="K17" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="L17" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="M17" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="N17" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="O17" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="P17" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="R17" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="S17" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="T17" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U17" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="V17" s="2">
+        <v>8</v>
+      </c>
+      <c r="W17" s="2">
+        <v>8</v>
+      </c>
+      <c r="X17" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="Z17" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="AB17" s="2">
+        <v>17.2</v>
+      </c>
+      <c r="AC17" s="2">
+        <v>145</v>
+      </c>
+      <c r="AD17" s="2">
+        <v>111</v>
+      </c>
+      <c r="AE17" s="2"/>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="2">
+        <v>23</v>
+      </c>
+      <c r="D18" s="2">
+        <v>7</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <v>23</v>
+      </c>
+      <c r="G18" s="2">
+        <v>6.3</v>
+      </c>
+      <c r="H18" s="2">
+        <v>20.9</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="J18" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="K18" s="2">
+        <v>14.6</v>
+      </c>
+      <c r="L18" s="2">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="M18" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="N18" s="2">
+        <v>6.3</v>
+      </c>
+      <c r="O18" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="P18" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>0</v>
+      </c>
+      <c r="R18" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="S18" s="2">
+        <v>0</v>
+      </c>
+      <c r="T18" s="2">
+        <v>0</v>
+      </c>
+      <c r="U18" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="V18" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="W18" s="2">
+        <v>6.3</v>
+      </c>
+      <c r="X18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="AA18" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="AB18" s="2">
+        <v>14.6</v>
+      </c>
+      <c r="AC18" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD18" s="2">
+        <v>120</v>
+      </c>
+      <c r="AE18" s="2"/>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="2">
+        <v>24</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2">
+        <v>22</v>
+      </c>
+      <c r="G19" s="2">
+        <v>13.1</v>
+      </c>
+      <c r="H19" s="2">
+        <v>19.7</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2">
+        <v>13.1</v>
+      </c>
+      <c r="N19" s="2">
+        <v>19.7</v>
+      </c>
+      <c r="O19" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="P19" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="R19" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="S19" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="T19" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="U19" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="V19" s="2">
+        <v>17.5</v>
+      </c>
+      <c r="W19" s="2">
+        <v>0</v>
+      </c>
+      <c r="X19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AA19" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="AB19" s="2">
+        <v>30.6</v>
+      </c>
+      <c r="AC19" s="2">
+        <v>120</v>
+      </c>
+      <c r="AD19" s="2">
+        <v>117</v>
+      </c>
+      <c r="AE19" s="2"/>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="2">
+        <v>24</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
+        <v>17</v>
+      </c>
+      <c r="G20" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="H20" s="2">
+        <v>22.6</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0</v>
+      </c>
+      <c r="K20" s="2">
+        <v>17</v>
+      </c>
+      <c r="L20" s="2">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="N20" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="O20" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="P20" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="R20" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="S20" s="2">
+        <v>1</v>
+      </c>
+      <c r="T20" s="2">
+        <v>11.3</v>
+      </c>
+      <c r="U20" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="V20" s="2">
+        <v>19.8</v>
+      </c>
+      <c r="W20" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="X20" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="2">
+        <v>11.3</v>
+      </c>
+      <c r="AC20" s="2">
+        <v>91</v>
+      </c>
+      <c r="AD20" s="2">
+        <v>117</v>
+      </c>
+      <c r="AE20" s="2"/>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="2">
+        <v>25</v>
+      </c>
+      <c r="D21" s="2">
+        <v>2</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2">
+        <v>13</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2">
+        <v>18.5</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2">
+        <v>18.5</v>
+      </c>
+      <c r="L21" s="2">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2">
+        <v>0</v>
+      </c>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>0</v>
+      </c>
+      <c r="R21" s="2">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2">
+        <v>0</v>
+      </c>
+      <c r="U21" s="2">
+        <v>7.4</v>
+      </c>
+      <c r="V21" s="2">
+        <v>7.4</v>
+      </c>
+      <c r="W21" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="X21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="AB21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="2">
+        <v>15</v>
+      </c>
+      <c r="AD21" s="2">
+        <v>118</v>
+      </c>
+      <c r="AE21" s="2"/>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="2">
+        <v>25</v>
+      </c>
+      <c r="D22" s="2">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2">
+        <v>4</v>
+      </c>
+      <c r="G22" s="2">
+        <v>24</v>
+      </c>
+      <c r="H22" s="2">
+        <v>24</v>
+      </c>
+      <c r="I22" s="2">
+        <v>1</v>
+      </c>
+      <c r="J22" s="2">
+        <v>12</v>
+      </c>
+      <c r="K22" s="2">
+        <v>12</v>
+      </c>
+      <c r="L22" s="2">
+        <v>1</v>
+      </c>
+      <c r="M22" s="2">
+        <v>12</v>
+      </c>
+      <c r="N22" s="2">
+        <v>12</v>
+      </c>
+      <c r="O22" s="2">
+        <v>1</v>
+      </c>
+      <c r="P22" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>0</v>
+      </c>
+      <c r="R22" s="2">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2">
+        <v>0</v>
+      </c>
+      <c r="U22" s="2">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2">
+        <v>0</v>
+      </c>
+      <c r="W22" s="2">
+        <v>12</v>
+      </c>
+      <c r="X22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="2">
+        <v>60.1</v>
+      </c>
+      <c r="AC22" s="2">
+        <v>246</v>
+      </c>
+      <c r="AD22" s="2">
+        <v>122</v>
+      </c>
+      <c r="AE22" s="2"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="https://www.basketball-reference.com/players/c/cunnica01.html" xr:uid="{636A26D3-1FB4-5940-9C4D-F352305260F9}"/>
+    <hyperlink ref="B3" r:id="rId2" display="https://www.basketball-reference.com/players/h/harrito02.html" xr:uid="{DAF18F76-0BCF-C04F-9912-3F774927DB26}"/>
+    <hyperlink ref="B4" r:id="rId3" display="https://www.basketball-reference.com/players/b/beaslma01.html" xr:uid="{10A4D5CD-7C15-564C-8428-2081E3A057D7}"/>
+    <hyperlink ref="AE4" r:id="rId4" location="all_smoy" display="https://www.basketball-reference.com/awards/awards_2025.html - all_smoy" xr:uid="{698D22A1-CBC9-344D-B83A-3E726B963B73}"/>
+    <hyperlink ref="B5" r:id="rId5" display="https://www.basketball-reference.com/players/h/hardati02.html" xr:uid="{FB560F25-1FFE-FE4A-A410-1C3FB274A8CE}"/>
+    <hyperlink ref="B6" r:id="rId6" display="https://www.basketball-reference.com/players/d/durenja01.html" xr:uid="{15C14E3A-A133-164D-8806-1450BC553654}"/>
+    <hyperlink ref="B7" r:id="rId7" display="https://www.basketball-reference.com/players/s/stewais01.html" xr:uid="{B3ACE12C-9B1E-6B46-A82F-6AE51BC61649}"/>
+    <hyperlink ref="B8" r:id="rId8" display="https://www.basketball-reference.com/players/t/thompau01.html" xr:uid="{FFDEE5E6-CD7E-6346-9C55-D4FAD4C5E18D}"/>
+    <hyperlink ref="B9" r:id="rId9" display="https://www.basketball-reference.com/players/h/hollaro01.html" xr:uid="{C1C56E18-CCC2-044C-A6A5-60D772931C49}"/>
+    <hyperlink ref="B10" r:id="rId10" display="https://www.basketball-reference.com/players/f/fontesi01.html" xr:uid="{7574DC55-8E35-F943-9772-036FC6727E71}"/>
+    <hyperlink ref="B11" r:id="rId11" display="https://www.basketball-reference.com/players/i/iveyja01.html" xr:uid="{549B5810-3E6C-E648-BF1E-5565A06EF650}"/>
+    <hyperlink ref="B12" r:id="rId12" display="https://www.basketball-reference.com/players/s/sassema01.html" xr:uid="{76CCCC87-EA3C-0946-8FF3-AAE9F7FA048B}"/>
+    <hyperlink ref="B13" r:id="rId13" display="https://www.basketball-reference.com/players/s/schrode01.html" xr:uid="{6A94BD1A-7080-4147-9007-0B7F83E165A2}"/>
+    <hyperlink ref="B14" r:id="rId14" display="https://www.basketball-reference.com/players/r/reedpa01.html" xr:uid="{970BA037-5CF3-C744-8A3A-A518B9CAC975}"/>
+    <hyperlink ref="B15" r:id="rId15" display="https://www.basketball-reference.com/players/m/moorewe01.html" xr:uid="{B5D4D582-5BF5-9549-AD1F-D831516B846D}"/>
+    <hyperlink ref="B16" r:id="rId16" display="https://www.basketball-reference.com/players/w/waterli01.html" xr:uid="{49303686-C2A1-F149-A655-F3E490A825A9}"/>
+    <hyperlink ref="B17" r:id="rId17" display="https://www.basketball-reference.com/players/k/klintbo01.html" xr:uid="{FD899FC9-C1DD-104E-B720-8C5C0EEFEA82}"/>
+    <hyperlink ref="B18" r:id="rId18" display="https://www.basketball-reference.com/players/j/jenkida01.html" xr:uid="{B204BAFB-15D4-3E48-B97B-996C0DAA5DC0}"/>
+    <hyperlink ref="B19" r:id="rId19" display="https://www.basketball-reference.com/players/s/smithto05.html" xr:uid="{6CDDBAE5-7AE2-AA43-89A8-1932C73325EC}"/>
+    <hyperlink ref="B20" r:id="rId20" display="https://www.basketball-reference.com/players/h/harpero02.html" xr:uid="{7285EAAC-D8CF-9A4D-8925-31CB593C9A26}"/>
+    <hyperlink ref="B21" r:id="rId21" display="https://www.basketball-reference.com/players/s/swideco01.html" xr:uid="{EE144C4B-DCFE-3E4C-ADE4-08612438D5B5}"/>
+    <hyperlink ref="B22" r:id="rId22" display="https://www.basketball-reference.com/players/w/willial06.html" xr:uid="{E2D6E2C8-60E0-224A-BE6B-22BC216CF5CF}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0053A506-3321-6341-BA3A-96184F5C04EE}">
+  <dimension ref="A1:AB22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2">
+        <v>70</v>
+      </c>
+      <c r="F2" s="2">
+        <v>70</v>
+      </c>
+      <c r="G2" s="2">
+        <v>2452</v>
+      </c>
+      <c r="H2" s="2">
+        <v>20.6</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0.254</v>
+      </c>
+      <c r="L2" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="M2" s="2">
+        <v>16.5</v>
+      </c>
+      <c r="N2" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="O2" s="2">
+        <v>43</v>
+      </c>
+      <c r="P2" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="R2" s="2">
+        <v>16</v>
+      </c>
+      <c r="S2" s="2">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="T2" s="2">
+        <v>3</v>
+      </c>
+      <c r="U2" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="V2" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="W2" s="2">
+        <v>0.115</v>
+      </c>
+      <c r="X2" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2">
+        <v>32</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="2">
+        <v>73</v>
+      </c>
+      <c r="F3" s="2">
+        <v>73</v>
+      </c>
+      <c r="G3" s="2">
+        <v>2305</v>
+      </c>
+      <c r="H3" s="2">
+        <v>13.9</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="L3" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="M3" s="2">
+        <v>17.5</v>
+      </c>
+      <c r="N3" s="2">
+        <v>10.4</v>
+      </c>
+      <c r="O3" s="2">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="P3" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="R3" s="2">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="S3" s="2">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="T3" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="U3" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="V3" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="W3" s="2">
+        <v>0.108</v>
+      </c>
+      <c r="X3" s="2">
+        <v>-0.5</v>
+      </c>
+      <c r="Y3" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="AA3" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="AB3" s="2"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2">
+        <v>28</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="8">
+        <v>82</v>
+      </c>
+      <c r="F4" s="2">
+        <v>18</v>
+      </c>
+      <c r="G4" s="2">
+        <v>2283</v>
+      </c>
+      <c r="H4" s="2">
+        <v>14.4</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0.59</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="L4" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M4" s="2">
+        <v>8</v>
+      </c>
+      <c r="N4" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="O4" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="P4" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="R4" s="2">
+        <v>6.8</v>
+      </c>
+      <c r="S4" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="T4" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="U4" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="V4" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="W4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="X4" s="2">
+        <v>2</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>-1.2</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="AA4" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="AB4" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2">
+        <v>32</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2">
+        <v>77</v>
+      </c>
+      <c r="F5" s="2">
+        <v>77</v>
+      </c>
+      <c r="G5" s="2">
+        <v>2153</v>
+      </c>
+      <c r="H5" s="2">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.56699999999999995</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="L5" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="M5" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="N5" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="O5" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="R5" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="S5" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="T5" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="U5" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="V5" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="W5" s="2">
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="X5" s="2">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="Y5" s="2">
+        <v>-0.9</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>-2.1</v>
+      </c>
+      <c r="AA5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="2"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2">
+        <v>21</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2">
+        <v>78</v>
+      </c>
+      <c r="F6" s="2">
+        <v>78</v>
+      </c>
+      <c r="G6" s="2">
+        <v>2034</v>
+      </c>
+      <c r="H6" s="2">
+        <v>21.4</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.70299999999999996</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0.443</v>
+      </c>
+      <c r="L6" s="2">
+        <v>15.2</v>
+      </c>
+      <c r="M6" s="2">
+        <v>28.7</v>
+      </c>
+      <c r="N6" s="2">
+        <v>22</v>
+      </c>
+      <c r="O6" s="2">
+        <v>14.7</v>
+      </c>
+      <c r="P6" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="R6" s="2">
+        <v>17.2</v>
+      </c>
+      <c r="S6" s="2">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="T6" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="U6" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="V6" s="2">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="W6" s="2">
+        <v>0.218</v>
+      </c>
+      <c r="X6" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="Y6" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="AB6" s="2"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="2">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2">
+        <v>72</v>
+      </c>
+      <c r="F7" s="2">
+        <v>4</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1434</v>
+      </c>
+      <c r="H7" s="2">
+        <v>14.6</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="L7" s="2">
+        <v>10.1</v>
+      </c>
+      <c r="M7" s="2">
+        <v>20.6</v>
+      </c>
+      <c r="N7" s="2">
+        <v>15.4</v>
+      </c>
+      <c r="O7" s="2">
+        <v>11.3</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>6.7</v>
+      </c>
+      <c r="R7" s="2">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="S7" s="2">
+        <v>12.4</v>
+      </c>
+      <c r="T7" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="U7" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="V7" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="W7" s="2">
+        <v>0.14399999999999999</v>
+      </c>
+      <c r="X7" s="2">
+        <v>-1.6</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="AB7" s="2"/>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="2">
+        <v>22</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2">
+        <v>59</v>
+      </c>
+      <c r="F8" s="2">
+        <v>48</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1328</v>
+      </c>
+      <c r="H8" s="2">
+        <v>17.2</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.56799999999999995</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.107</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0.309</v>
+      </c>
+      <c r="L8" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="M8" s="2">
+        <v>15.9</v>
+      </c>
+      <c r="N8" s="2">
+        <v>12.6</v>
+      </c>
+      <c r="O8" s="2">
+        <v>14.4</v>
+      </c>
+      <c r="P8" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="R8" s="2">
+        <v>13.3</v>
+      </c>
+      <c r="S8" s="2">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="T8" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="U8" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="V8" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="W8" s="2">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="X8" s="2">
+        <v>-0.8</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="AB8" s="2"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="2">
+        <v>19</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="2">
+        <v>81</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1266</v>
+      </c>
+      <c r="H9" s="2">
+        <v>11.1</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.36299999999999999</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0.29299999999999998</v>
+      </c>
+      <c r="L9" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="M9" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="N9" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="O9" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="P9" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="R9" s="2">
+        <v>13.3</v>
+      </c>
+      <c r="S9" s="2">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="T9" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="U9" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="V9" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="W9" s="2">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="X9" s="2">
+        <v>-3.3</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>-3</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>-0.3</v>
+      </c>
+      <c r="AB9" s="2"/>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="2">
+        <v>29</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="2">
+        <v>75</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1237</v>
+      </c>
+      <c r="H10" s="2">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0.54400000000000004</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="K10" s="2">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="L10" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="M10" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="N10" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="O10" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="P10" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="R10" s="2">
+        <v>11.6</v>
+      </c>
+      <c r="S10" s="2">
+        <v>15.8</v>
+      </c>
+      <c r="T10" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="U10" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="V10" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="W10" s="2">
+        <v>6.3E-2</v>
+      </c>
+      <c r="X10" s="2">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>-0.7</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>-2.9</v>
+      </c>
+      <c r="AA10" s="2">
+        <v>-0.3</v>
+      </c>
+      <c r="AB10" s="2"/>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="2">
+        <v>22</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2">
+        <v>30</v>
+      </c>
+      <c r="F11" s="2">
+        <v>30</v>
+      </c>
+      <c r="G11" s="2">
+        <v>898</v>
+      </c>
+      <c r="H11" s="2">
+        <v>14.7</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0.56899999999999995</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.373</v>
+      </c>
+      <c r="K11" s="2">
+        <v>0.28100000000000003</v>
+      </c>
+      <c r="L11" s="2">
+        <v>5</v>
+      </c>
+      <c r="M11" s="2">
+        <v>10.3</v>
+      </c>
+      <c r="N11" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="O11" s="2">
+        <v>19.7</v>
+      </c>
+      <c r="P11" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="R11" s="2">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="S11" s="2">
+        <v>26</v>
+      </c>
+      <c r="T11" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="U11" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="V11" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="W11" s="2">
+        <v>6.2E-2</v>
+      </c>
+      <c r="X11" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>-0.8</v>
+      </c>
+      <c r="Z11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AB11" s="2"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="2">
+        <v>24</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2">
+        <v>57</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2">
+        <v>811</v>
+      </c>
+      <c r="H12" s="2">
+        <v>14</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0.58899999999999997</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0.51400000000000001</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="L12" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="M12" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="N12" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="O12" s="2">
+        <v>22.9</v>
+      </c>
+      <c r="P12" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="R12" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="S12" s="2">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="T12" s="2">
+        <v>1</v>
+      </c>
+      <c r="U12" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="V12" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="W12" s="2">
+        <v>0.108</v>
+      </c>
+      <c r="X12" s="2">
+        <v>-0.4</v>
+      </c>
+      <c r="Y12" s="2">
+        <v>-0.2</v>
+      </c>
+      <c r="Z12" s="2">
+        <v>-0.6</v>
+      </c>
+      <c r="AA12" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="AB12" s="2"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="2">
+        <v>31</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2">
+        <v>28</v>
+      </c>
+      <c r="F13" s="2">
+        <v>8</v>
+      </c>
+      <c r="G13" s="2">
+        <v>705</v>
+      </c>
+      <c r="H13" s="2">
+        <v>12.9</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0.42199999999999999</v>
+      </c>
+      <c r="K13" s="2">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="L13" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="M13" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="N13" s="2">
+        <v>5.8</v>
+      </c>
+      <c r="O13" s="2">
+        <v>27.8</v>
+      </c>
+      <c r="P13" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="R13" s="2">
+        <v>10.7</v>
+      </c>
+      <c r="S13" s="2">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="T13" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="U13" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="V13" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="W13" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="X13" s="2">
+        <v>-0.9</v>
+      </c>
+      <c r="Y13" s="2">
+        <v>-1.2</v>
+      </c>
+      <c r="Z13" s="2">
+        <v>-2.1</v>
+      </c>
+      <c r="AA13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="2"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="2">
+        <v>25</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="2">
+        <v>45</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>438</v>
+      </c>
+      <c r="H14" s="2">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0.57299999999999995</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0.19700000000000001</v>
+      </c>
+      <c r="K14" s="2">
+        <v>0.29599999999999999</v>
+      </c>
+      <c r="L14" s="2">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="M14" s="2">
+        <v>20.8</v>
+      </c>
+      <c r="N14" s="2">
+        <v>15.6</v>
+      </c>
+      <c r="O14" s="2">
+        <v>14</v>
+      </c>
+      <c r="P14" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="R14" s="2">
+        <v>13.9</v>
+      </c>
+      <c r="S14" s="2">
+        <v>18</v>
+      </c>
+      <c r="T14" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="U14" s="2">
+        <v>1</v>
+      </c>
+      <c r="V14" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="W14" s="2">
+        <v>0.17299999999999999</v>
+      </c>
+      <c r="X14" s="2">
+        <v>-1.2</v>
+      </c>
+      <c r="Y14" s="2">
+        <v>4</v>
+      </c>
+      <c r="Z14" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="AA14" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AB14" s="2"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="2">
+        <v>23</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="2">
+        <v>20</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>219</v>
+      </c>
+      <c r="H15" s="2">
+        <v>12.4</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="K15" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="L15" s="2">
+        <v>5.6</v>
+      </c>
+      <c r="M15" s="2">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="N15" s="2">
+        <v>11.1</v>
+      </c>
+      <c r="O15" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="P15" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="R15" s="2">
+        <v>13.8</v>
+      </c>
+      <c r="S15" s="2">
+        <v>12.6</v>
+      </c>
+      <c r="T15" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="U15" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="V15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="W15" s="2">
+        <v>0.115</v>
+      </c>
+      <c r="X15" s="2">
+        <v>-1.7</v>
+      </c>
+      <c r="Y15" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="Z15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="AB15" s="2"/>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="2">
+        <v>27</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="2">
+        <v>14</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
+        <v>123</v>
+      </c>
+      <c r="H16" s="2">
+        <v>11</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="K16" s="2">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="M16" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="N16" s="2">
+        <v>6.3</v>
+      </c>
+      <c r="O16" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="P16" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="R16" s="2">
+        <v>6.4</v>
+      </c>
+      <c r="S16" s="2">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="T16" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="U16" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="V16" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="W16" s="2">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="X16" s="2">
+        <v>-0.5</v>
+      </c>
+      <c r="Y16" s="2">
+        <v>-0.7</v>
+      </c>
+      <c r="Z16" s="2">
+        <v>-1.2</v>
+      </c>
+      <c r="AA16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="2"/>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="2">
+        <v>21</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="2">
+        <v>8</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
+        <v>42</v>
+      </c>
+      <c r="H17" s="2">
+        <v>15.9</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0.68899999999999995</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="K17" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="L17" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="M17" s="2">
+        <v>15.7</v>
+      </c>
+      <c r="N17" s="2">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="O17" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="P17" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="R17" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="S17" s="2">
+        <v>11.9</v>
+      </c>
+      <c r="T17" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="U17" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="V17" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="W17" s="2">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="X17" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="Z17" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="2"/>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="2">
+        <v>23</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="2">
+        <v>7</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
+        <v>23</v>
+      </c>
+      <c r="H18" s="2">
+        <v>-0.1</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0.32200000000000001</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="K18" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="L18" s="2">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="N18" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="O18" s="2">
+        <v>17.3</v>
+      </c>
+      <c r="P18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>0</v>
+      </c>
+      <c r="R18" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="S18" s="2">
+        <v>21.8</v>
+      </c>
+      <c r="T18" s="2">
+        <v>-0.1</v>
+      </c>
+      <c r="U18" s="2">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2">
+        <v>-0.1</v>
+      </c>
+      <c r="W18" s="2">
+        <v>-0.15</v>
+      </c>
+      <c r="X18" s="2">
+        <v>-10.199999999999999</v>
+      </c>
+      <c r="Y18" s="2">
+        <v>-5.7</v>
+      </c>
+      <c r="Z18" s="2">
+        <v>-15.8</v>
+      </c>
+      <c r="AA18" s="2">
+        <v>-0.1</v>
+      </c>
+      <c r="AB18" s="2"/>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="2">
+        <v>24</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2">
+        <v>22</v>
+      </c>
+      <c r="H19" s="2">
+        <v>19.5</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0.67800000000000005</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="L19" s="2">
+        <v>20.3</v>
+      </c>
+      <c r="M19" s="2">
+        <v>20</v>
+      </c>
+      <c r="N19" s="2">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="O19" s="2">
+        <v>0</v>
+      </c>
+      <c r="P19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>0</v>
+      </c>
+      <c r="R19" s="2">
+        <v>16.2</v>
+      </c>
+      <c r="S19" s="2">
+        <v>23.6</v>
+      </c>
+      <c r="T19" s="2">
+        <v>0</v>
+      </c>
+      <c r="U19" s="2">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="W19" s="2">
+        <v>0.128</v>
+      </c>
+      <c r="X19" s="2">
+        <v>-2.4</v>
+      </c>
+      <c r="Y19" s="2">
+        <v>-6.5</v>
+      </c>
+      <c r="Z19" s="2">
+        <v>-8.9</v>
+      </c>
+      <c r="AA19" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="2"/>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="2">
+        <v>24</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2">
+        <v>17</v>
+      </c>
+      <c r="H20" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="K20" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="L20" s="2">
+        <v>26.3</v>
+      </c>
+      <c r="M20" s="2">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="N20" s="2">
+        <v>22.8</v>
+      </c>
+      <c r="O20" s="2">
+        <v>14.3</v>
+      </c>
+      <c r="P20" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>0</v>
+      </c>
+      <c r="R20" s="2">
+        <v>0</v>
+      </c>
+      <c r="S20" s="2">
+        <v>22</v>
+      </c>
+      <c r="T20" s="2">
+        <v>0</v>
+      </c>
+      <c r="U20" s="2">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2">
+        <v>0</v>
+      </c>
+      <c r="W20" s="2">
+        <v>-0.06</v>
+      </c>
+      <c r="X20" s="2">
+        <v>-5.5</v>
+      </c>
+      <c r="Y20" s="2">
+        <v>-9.1999999999999993</v>
+      </c>
+      <c r="Z20" s="2">
+        <v>-14.7</v>
+      </c>
+      <c r="AA20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="2"/>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="2">
+        <v>25</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="2">
+        <v>2</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
+        <v>13</v>
+      </c>
+      <c r="H21" s="2">
+        <v>-11</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
+        <v>1</v>
+      </c>
+      <c r="K21" s="2">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="N21" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="O21" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="P21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>0</v>
+      </c>
+      <c r="R21" s="2">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2">
+        <v>16.2</v>
+      </c>
+      <c r="T21" s="2">
+        <v>-0.1</v>
+      </c>
+      <c r="U21" s="2">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2">
+        <v>-0.1</v>
+      </c>
+      <c r="W21" s="2">
+        <v>-0.316</v>
+      </c>
+      <c r="X21" s="2">
+        <v>-14.6</v>
+      </c>
+      <c r="Y21" s="2">
+        <v>-5.8</v>
+      </c>
+      <c r="Z21" s="2">
+        <v>-20.399999999999999</v>
+      </c>
+      <c r="AA21" s="2">
+        <v>-0.1</v>
+      </c>
+      <c r="AB21" s="2"/>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="2">
+        <v>25</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2">
+        <v>4</v>
+      </c>
+      <c r="H22" s="2">
+        <v>53.4</v>
+      </c>
+      <c r="I22" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="K22" s="2">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2">
+        <v>0</v>
+      </c>
+      <c r="O22" s="2">
+        <v>65</v>
+      </c>
+      <c r="P22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>0</v>
+      </c>
+      <c r="R22" s="2">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2">
+        <v>21.1</v>
+      </c>
+      <c r="T22" s="2">
+        <v>0</v>
+      </c>
+      <c r="U22" s="2">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2">
+        <v>0</v>
+      </c>
+      <c r="W22" s="2">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="X22" s="2">
+        <v>37.9</v>
+      </c>
+      <c r="Y22" s="2">
+        <v>6.2</v>
+      </c>
+      <c r="Z22" s="2">
+        <v>44.1</v>
+      </c>
+      <c r="AA22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="2"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="https://www.basketball-reference.com/players/c/cunnica01.html" xr:uid="{485834F0-2B90-2A4D-BC42-74FA235FEC35}"/>
+    <hyperlink ref="B3" r:id="rId2" display="https://www.basketball-reference.com/players/h/harrito02.html" xr:uid="{EE830211-427C-D94E-84B3-AF9DAFD7E48D}"/>
+    <hyperlink ref="B4" r:id="rId3" display="https://www.basketball-reference.com/players/b/beaslma01.html" xr:uid="{76A3B2D7-240B-0949-821B-3ADEBE1AC747}"/>
+    <hyperlink ref="AB4" r:id="rId4" location="all_smoy" display="https://www.basketball-reference.com/awards/awards_2025.html - all_smoy" xr:uid="{0BEBEEA3-7DDC-6146-A581-1A0BEE22FD5F}"/>
+    <hyperlink ref="B5" r:id="rId5" display="https://www.basketball-reference.com/players/h/hardati02.html" xr:uid="{4939F011-2151-3043-ACEA-1F5A1FE5AE7A}"/>
+    <hyperlink ref="B6" r:id="rId6" display="https://www.basketball-reference.com/players/d/durenja01.html" xr:uid="{0546EF07-8B4E-8C43-83ED-BB88FF91C8E6}"/>
+    <hyperlink ref="B7" r:id="rId7" display="https://www.basketball-reference.com/players/s/stewais01.html" xr:uid="{FE2BCEE9-43A8-DA4F-B64E-AD0C35626CE0}"/>
+    <hyperlink ref="B8" r:id="rId8" display="https://www.basketball-reference.com/players/t/thompau01.html" xr:uid="{B2BF4C4C-0BFD-7B42-A511-FA1DBE6CC1A9}"/>
+    <hyperlink ref="B9" r:id="rId9" display="https://www.basketball-reference.com/players/h/hollaro01.html" xr:uid="{8BF3522E-1D9E-A540-9C36-2FB426FADE55}"/>
+    <hyperlink ref="B10" r:id="rId10" display="https://www.basketball-reference.com/players/f/fontesi01.html" xr:uid="{B9D7C5EC-9F7A-9A45-A114-13FF6BACC827}"/>
+    <hyperlink ref="B11" r:id="rId11" display="https://www.basketball-reference.com/players/i/iveyja01.html" xr:uid="{C82417B2-0467-D142-B342-EEBDCA696D65}"/>
+    <hyperlink ref="B12" r:id="rId12" display="https://www.basketball-reference.com/players/s/sassema01.html" xr:uid="{EC05287C-E998-5B41-8A92-84B5FEEBA1A3}"/>
+    <hyperlink ref="B13" r:id="rId13" display="https://www.basketball-reference.com/players/s/schrode01.html" xr:uid="{EA2C01BE-64EF-3944-9EBC-AFC836001BAC}"/>
+    <hyperlink ref="B14" r:id="rId14" display="https://www.basketball-reference.com/players/r/reedpa01.html" xr:uid="{6517A2C3-EAE5-3042-8A87-2A21DCDBFA40}"/>
+    <hyperlink ref="B15" r:id="rId15" display="https://www.basketball-reference.com/players/m/moorewe01.html" xr:uid="{25D95B00-141A-3E44-9B10-769E30A5151F}"/>
+    <hyperlink ref="B16" r:id="rId16" display="https://www.basketball-reference.com/players/w/waterli01.html" xr:uid="{E0D0D243-FB92-E74A-8C75-F1110A9462C8}"/>
+    <hyperlink ref="B17" r:id="rId17" display="https://www.basketball-reference.com/players/k/klintbo01.html" xr:uid="{5F5E28AB-504F-0D43-BC80-B80C4C7472F6}"/>
+    <hyperlink ref="B18" r:id="rId18" display="https://www.basketball-reference.com/players/j/jenkida01.html" xr:uid="{64298C6D-A49F-8247-953C-A0017DACE245}"/>
+    <hyperlink ref="B19" r:id="rId19" display="https://www.basketball-reference.com/players/s/smithto05.html" xr:uid="{460C87CA-2812-7048-B9DF-56156019E486}"/>
+    <hyperlink ref="B20" r:id="rId20" display="https://www.basketball-reference.com/players/h/harpero02.html" xr:uid="{039A4FCD-A62F-AB45-8248-388BB3C2856C}"/>
+    <hyperlink ref="B21" r:id="rId21" display="https://www.basketball-reference.com/players/s/swideco01.html" xr:uid="{343089CE-2543-4640-91E1-D2319303861D}"/>
+    <hyperlink ref="B22" r:id="rId22" display="https://www.basketball-reference.com/players/w/willial06.html" xr:uid="{32835979-4E29-8A4D-95DE-AFAD4A11E489}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D9C64A8-6CA5-0644-A1B1-319461B00C21}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>